--- a/databases/metricas_avaliacao_clusters.xlsx
+++ b/databases/metricas_avaliacao_clusters.xlsx
@@ -403,22 +403,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7941069971283413</v>
+        <v>0.7921386638930618</v>
       </c>
       <c r="C2">
-        <v>0.9698700015920991</v>
+        <v>0.9656836697298948</v>
       </c>
       <c r="D2">
         <v>0.001594896331738431</v>
       </c>
       <c r="E2">
-        <v>0.6958733253577559</v>
+        <v>0.6962785504213564</v>
       </c>
       <c r="F2">
-        <v>8062.97342540988</v>
+        <v>8109.234314366015</v>
       </c>
       <c r="G2">
-        <v>9633.290544473339</v>
+        <v>9695.03555022506</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -433,22 +433,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.7420301852618171</v>
+        <v>0.7409590842431715</v>
       </c>
       <c r="C3">
-        <v>0.852250640736768</v>
+        <v>0.8473853207615423</v>
       </c>
       <c r="D3">
         <v>0.001715265866209264</v>
       </c>
       <c r="E3">
-        <v>0.7111539044691423</v>
+        <v>0.7115145972499541</v>
       </c>
       <c r="F3">
-        <v>10313.28715706212</v>
+        <v>10382.20471462729</v>
       </c>
       <c r="G3">
-        <v>12573.21527936072</v>
+        <v>12675.40697608507</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -463,22 +463,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.7336926191776074</v>
+        <v>0.7332471668662663</v>
       </c>
       <c r="C4">
-        <v>0.865662558508083</v>
+        <v>0.860316877404434</v>
       </c>
       <c r="D4">
         <v>0.001766784452296813</v>
       </c>
       <c r="E4">
-        <v>0.7086888294100762</v>
+        <v>0.7090514933228995</v>
       </c>
       <c r="F4">
-        <v>9709.787234853789</v>
+        <v>9782.009177852766</v>
       </c>
       <c r="G4">
-        <v>11610.13017728958</v>
+        <v>11721.80198026232</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7458629981298873</v>
+        <v>0.7424733057440944</v>
       </c>
       <c r="C5">
-        <v>0.9378124923791673</v>
+        <v>0.9341181358009374</v>
       </c>
       <c r="D5">
-        <v>0.001828153564899453</v>
+        <v>0.00181488203266787</v>
       </c>
       <c r="E5">
-        <v>0.7174752056770378</v>
+        <v>0.7168033615433581</v>
       </c>
       <c r="F5">
-        <v>9673.268714747495</v>
+        <v>9412.567879535103</v>
       </c>
       <c r="G5">
-        <v>11314.07875019638</v>
+        <v>10991.33537419847</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.748597769168126</v>
+        <v>0.7290653489051589</v>
       </c>
       <c r="C6">
-        <v>0.961271620131613</v>
+        <v>0.9108856787515828</v>
       </c>
       <c r="D6">
-        <v>0.001937984496124024</v>
+        <v>0.001834862385321094</v>
       </c>
       <c r="E6">
-        <v>0.7252054629014772</v>
+        <v>0.7236426044474198</v>
       </c>
       <c r="F6">
-        <v>11260.50430122014</v>
+        <v>8411.112067538839</v>
       </c>
       <c r="G6">
-        <v>13104.23769653571</v>
+        <v>9781.47507323989</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7201452044264669</v>
+        <v>0.7183591274932485</v>
       </c>
       <c r="C7">
-        <v>0.7897485784321021</v>
+        <v>0.7860424993761649</v>
       </c>
       <c r="D7">
         <v>0.001666666666666661</v>
       </c>
       <c r="E7">
-        <v>0.7420467099573532</v>
+        <v>0.7420273857319543</v>
       </c>
       <c r="F7">
-        <v>10281.6413626909</v>
+        <v>10316.50312925316</v>
       </c>
       <c r="G7">
-        <v>10706.96282543698</v>
+        <v>10741.80402207091</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.7510915564717757</v>
+        <v>0.7505295310804454</v>
       </c>
       <c r="C8">
-        <v>0.8866966415312879</v>
+        <v>0.8734997492287507</v>
       </c>
       <c r="D8">
-        <v>0.00179856115107913</v>
+        <v>0.001795332136445244</v>
       </c>
       <c r="E8">
-        <v>0.7198038755771549</v>
+        <v>0.7199106460213437</v>
       </c>
       <c r="F8">
-        <v>11685.59996623936</v>
+        <v>11727.42992223991</v>
       </c>
       <c r="G8">
-        <v>13294.55292056119</v>
+        <v>13361.27192016878</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.7558855278715617</v>
+        <v>0.7615978523819178</v>
       </c>
       <c r="C9">
-        <v>0.9547006172040674</v>
+        <v>0.942774051430089</v>
       </c>
       <c r="D9">
-        <v>0.002016129032258057</v>
+        <v>0.002004008016032066</v>
       </c>
       <c r="E9">
-        <v>0.7217028898186665</v>
+        <v>0.7216899676452846</v>
       </c>
       <c r="F9">
-        <v>13068.71162041135</v>
+        <v>13023.63781900941</v>
       </c>
       <c r="G9">
-        <v>15077.19029248069</v>
+        <v>15141.52070482313</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.5856783331102879</v>
+        <v>0.5825913203616401</v>
       </c>
       <c r="C10">
-        <v>0.6398184129959058</v>
+        <v>0.6376043147213164</v>
       </c>
       <c r="D10">
         <v>0.003984063745019906</v>
       </c>
       <c r="E10">
-        <v>0.7206640131454861</v>
+        <v>0.7204560891611551</v>
       </c>
       <c r="F10">
-        <v>16445.76015979713</v>
+        <v>16587.42630116144</v>
       </c>
       <c r="G10">
-        <v>19138.87196716154</v>
+        <v>19198.94995451903</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.5848393160660391</v>
+        <v>0.5825055690645841</v>
       </c>
       <c r="C11">
-        <v>0.6608595957387632</v>
+        <v>0.6536829015094212</v>
       </c>
       <c r="D11">
         <v>0.003984063745019906</v>
       </c>
       <c r="E11">
-        <v>0.7181131935473488</v>
+        <v>0.7182137294561327</v>
       </c>
       <c r="F11">
-        <v>20456.57438916304</v>
+        <v>20636.97660213238</v>
       </c>
       <c r="G11">
-        <v>23523.62330836613</v>
+        <v>23805.65466837364</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.7071160891048286</v>
+        <v>0.7053803477032572</v>
       </c>
       <c r="C12">
-        <v>0.7600670576393588</v>
+        <v>0.7564631773331069</v>
       </c>
       <c r="D12">
         <v>0.001680672268907557</v>
       </c>
       <c r="E12">
-        <v>0.7450465831222597</v>
+        <v>0.7449461241127394</v>
       </c>
       <c r="F12">
-        <v>10219.71883090043</v>
+        <v>10246.45050768732</v>
       </c>
       <c r="G12">
-        <v>10343.90999708814</v>
+        <v>10367.36273918394</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -733,22 +733,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.7819523670823411</v>
+        <v>0.7800664596414588</v>
       </c>
       <c r="C13">
-        <v>0.9416378409377564</v>
+        <v>0.9363643663653314</v>
       </c>
       <c r="D13">
         <v>0.001680672268907557</v>
       </c>
       <c r="E13">
-        <v>0.6879117916236731</v>
+        <v>0.6883586903922368</v>
       </c>
       <c r="F13">
-        <v>8920.469200580463</v>
+        <v>8985.697260377401</v>
       </c>
       <c r="G13">
-        <v>10805.39101522825</v>
+        <v>10897.55806299406</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.748048988778814</v>
+        <v>0.7506189534028507</v>
       </c>
       <c r="C14">
-        <v>0.8991450799132934</v>
+        <v>0.9191916800215086</v>
       </c>
       <c r="D14">
         <v>0.001953124999999993</v>
       </c>
       <c r="E14">
-        <v>0.7100172886641353</v>
+        <v>0.7100629162544673</v>
       </c>
       <c r="F14">
-        <v>12485.30141232235</v>
+        <v>12473.90242804929</v>
       </c>
       <c r="G14">
-        <v>14409.00250696343</v>
+        <v>14311.13603291362</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.5683805860633697</v>
+        <v>0.5656024372176113</v>
       </c>
       <c r="C15">
-        <v>0.6323218400591986</v>
+        <v>0.6257846277592742</v>
       </c>
       <c r="D15">
         <v>0.003984063745019906</v>
       </c>
       <c r="E15">
-        <v>0.710149974489791</v>
+        <v>0.7100889731900483</v>
       </c>
       <c r="F15">
-        <v>15575.81885903143</v>
+        <v>15662.34535734599</v>
       </c>
       <c r="G15">
-        <v>17765.40204013872</v>
+        <v>17904.07075757172</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.5954961683593516</v>
+        <v>0.5928858433194888</v>
       </c>
       <c r="C16">
-        <v>0.6808177018982697</v>
+        <v>0.6724545072721113</v>
       </c>
       <c r="D16">
         <v>0.003984063745019906</v>
       </c>
       <c r="E16">
-        <v>0.7102923817263634</v>
+        <v>0.7105629453110597</v>
       </c>
       <c r="F16">
-        <v>18145.84483130118</v>
+        <v>18337.79243504147</v>
       </c>
       <c r="G16">
-        <v>20198.72490095205</v>
+        <v>20465.34502241612</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -853,22 +853,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.09811726516898804</v>
+        <v>0.09788433563054418</v>
       </c>
       <c r="C17">
-        <v>0.1174139167798748</v>
+        <v>0.1171797793816212</v>
       </c>
       <c r="D17">
         <v>0.3130252100840336</v>
       </c>
       <c r="E17">
-        <v>0.9320719076795019</v>
+        <v>0.9322552304793569</v>
       </c>
       <c r="F17">
-        <v>411.9554488308174</v>
+        <v>414.6981733148527</v>
       </c>
       <c r="G17">
-        <v>352.3978899943585</v>
+        <v>354.5385277928403</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -883,22 +883,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.2147727843112944</v>
+        <v>0.2146482440885665</v>
       </c>
       <c r="C18">
-        <v>0.2650556908938559</v>
+        <v>0.2649332763876824</v>
       </c>
       <c r="D18">
         <v>0.3151125401929259</v>
       </c>
       <c r="E18">
-        <v>0.8935053748094735</v>
+        <v>0.8938425208602352</v>
       </c>
       <c r="F18">
-        <v>356.5848766396952</v>
+        <v>359.0953714209782</v>
       </c>
       <c r="G18">
-        <v>307.1517160718903</v>
+        <v>309.1030665340019</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.1078960254630286</v>
+        <v>0.1077026866909191</v>
       </c>
       <c r="C19">
-        <v>0.142125283332104</v>
+        <v>0.1419581126004041</v>
       </c>
       <c r="D19">
         <v>0.2122186495176849</v>
       </c>
       <c r="E19">
-        <v>0.8863858590672992</v>
+        <v>0.8867424995401773</v>
       </c>
       <c r="F19">
-        <v>238.3148843262178</v>
+        <v>239.9931130639536</v>
       </c>
       <c r="G19">
-        <v>205.4637953848905</v>
+        <v>206.7695911977547</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.0901125458778273</v>
+        <v>0.08979748823712735</v>
       </c>
       <c r="C20">
-        <v>0.09672253883738814</v>
+        <v>0.09641883286624867</v>
       </c>
       <c r="D20">
         <v>0.112540192926045</v>
       </c>
       <c r="E20">
-        <v>0.8861031152109551</v>
+        <v>0.886459704912805</v>
       </c>
       <c r="F20">
-        <v>178.8029098811049</v>
+        <v>180.0621093224045</v>
       </c>
       <c r="G20">
-        <v>154.2247559271684</v>
+        <v>155.2050058160424</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.1220961820212341</v>
+        <v>0.1111660533155121</v>
       </c>
       <c r="C21">
-        <v>0.1280274110821686</v>
+        <v>0.1174147798005934</v>
       </c>
       <c r="D21">
-        <v>0.04905660377358493</v>
+        <v>0.04912280701754381</v>
       </c>
       <c r="E21">
-        <v>0.8311822064066956</v>
+        <v>0.838298757762344</v>
       </c>
       <c r="F21">
-        <v>201.1758289251678</v>
+        <v>175.1997006219439</v>
       </c>
       <c r="G21">
-        <v>176.0954538847682</v>
+        <v>152.2744222528795</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.3038224012989404</v>
+        <v>0.3035014612166439</v>
       </c>
       <c r="C22">
-        <v>0.3422118509126172</v>
+        <v>0.3418961777605273</v>
       </c>
       <c r="D22">
         <v>0.3151125401929259</v>
       </c>
       <c r="E22">
-        <v>0.9137829586790857</v>
+        <v>0.914049344840546</v>
       </c>
       <c r="F22">
-        <v>679.052777815384</v>
+        <v>683.8129655465774</v>
       </c>
       <c r="G22">
-        <v>584.6214685171649</v>
+        <v>588.3170937312703</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.4676693607677068</v>
+        <v>0.4413146668735033</v>
       </c>
       <c r="C23">
-        <v>0.5098351411084578</v>
+        <v>0.5099334292151916</v>
       </c>
       <c r="D23">
-        <v>0.003984063745019977</v>
+        <v>0.0199203187250996</v>
       </c>
       <c r="E23">
-        <v>0.7377133860967758</v>
+        <v>0.7896402423141253</v>
       </c>
       <c r="F23">
-        <v>3816.205661906449</v>
+        <v>865.034424258139</v>
       </c>
       <c r="G23">
-        <v>2826.750655711593</v>
+        <v>782.7477138605682</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.3713754821589448</v>
+        <v>0.3035036705526018</v>
       </c>
       <c r="C24">
-        <v>0.4142051405771846</v>
+        <v>0.353742100141515</v>
       </c>
       <c r="D24">
-        <v>0.005050505050505122</v>
+        <v>0.02512562814070352</v>
       </c>
       <c r="E24">
-        <v>0.7372695887299486</v>
+        <v>0.7897301568202093</v>
       </c>
       <c r="F24">
-        <v>2594.95375592819</v>
+        <v>592.2712032302167</v>
       </c>
       <c r="G24">
-        <v>1917.322601716682</v>
+        <v>535.1718334699847</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1093,22 +1093,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.380217787654952</v>
+        <v>0.417301610174766</v>
       </c>
       <c r="C25">
-        <v>0.418091645951883</v>
+        <v>0.449286915172545</v>
       </c>
       <c r="D25">
-        <v>0.00877192982456153</v>
+        <v>0.007874015748031539</v>
       </c>
       <c r="E25">
-        <v>0.7205539584925527</v>
+        <v>0.7280126377645855</v>
       </c>
       <c r="F25">
-        <v>2120.719767435529</v>
+        <v>4483.106811983894</v>
       </c>
       <c r="G25">
-        <v>1548.526040890759</v>
+        <v>3915.764066549737</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4409108665839517</v>
+        <v>0.4741782697889286</v>
       </c>
       <c r="C26">
-        <v>0.4774146083058366</v>
+        <v>0.5156359733455057</v>
       </c>
       <c r="D26">
-        <v>0.008928571428571556</v>
+        <v>0.009345794392523412</v>
       </c>
       <c r="E26">
-        <v>0.6936587588707978</v>
+        <v>0.6908633954396576</v>
       </c>
       <c r="F26">
-        <v>1785.885298581713</v>
+        <v>4507.767724189112</v>
       </c>
       <c r="G26">
-        <v>1296.064717520166</v>
+        <v>3735.380668741548</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.4686024942304404</v>
+        <v>0.4220732461249934</v>
       </c>
       <c r="C27">
-        <v>0.6638586856928255</v>
+        <v>0.4498079282799691</v>
       </c>
       <c r="D27">
-        <v>0.03403141361256546</v>
+        <v>0.038781163434903</v>
       </c>
       <c r="E27">
-        <v>0.883273379583486</v>
+        <v>0.8962282144145611</v>
       </c>
       <c r="F27">
-        <v>874.8514868835268</v>
+        <v>782.7634117339105</v>
       </c>
       <c r="G27">
-        <v>736.979205489239</v>
+        <v>685.3112220795941</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.3248229198334152</v>
+        <v>0.3125424208524248</v>
       </c>
       <c r="C28">
-        <v>0.3702666044674546</v>
+        <v>0.4185968610906735</v>
       </c>
       <c r="D28">
-        <v>0.04905660377358493</v>
+        <v>0.04912280701754381</v>
       </c>
       <c r="E28">
-        <v>0.8595782764471059</v>
+        <v>0.8723621734205375</v>
       </c>
       <c r="F28">
-        <v>488.8084063085658</v>
+        <v>428.9921101569612</v>
       </c>
       <c r="G28">
-        <v>426.7008752984581</v>
+        <v>370.997349530146</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1213,22 +1213,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.2671872146923461</v>
+        <v>0.4332066054843731</v>
       </c>
       <c r="C29">
-        <v>0.3549902737871833</v>
+        <v>0.4960995890416366</v>
       </c>
       <c r="D29">
-        <v>0.04905660377358493</v>
+        <v>0.005649717514124273</v>
       </c>
       <c r="E29">
-        <v>0.831514781250421</v>
+        <v>0.7333631821407731</v>
       </c>
       <c r="F29">
-        <v>334.5748050198121</v>
+        <v>2727.72603995589</v>
       </c>
       <c r="G29">
-        <v>292.5771855591126</v>
+        <v>2014.473508603711</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.3640603931875296</v>
+        <v>0.3567137252070376</v>
       </c>
       <c r="C30">
-        <v>0.4445158492846142</v>
+        <v>0.4399384965470529</v>
       </c>
       <c r="D30">
-        <v>0.006493506493506471</v>
+        <v>0.005747126436781589</v>
       </c>
       <c r="E30">
-        <v>0.7289342884166479</v>
+        <v>0.7308181288333772</v>
       </c>
       <c r="F30">
-        <v>2113.650591453974</v>
+        <v>2063.861669336371</v>
       </c>
       <c r="G30">
-        <v>1561.259628940038</v>
+        <v>1524.856654985365</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4222288091246418</v>
+        <v>0.4127182840288467</v>
       </c>
       <c r="C31">
-        <v>0.4888796032842361</v>
+        <v>0.4955497421433226</v>
       </c>
       <c r="D31">
         <v>0.009090909090909059</v>
       </c>
       <c r="E31">
-        <v>0.6967792540664742</v>
+        <v>0.697028718967043</v>
       </c>
       <c r="F31">
-        <v>1848.602976678229</v>
+        <v>1822.9624769826</v>
       </c>
       <c r="G31">
-        <v>1350.219366201652</v>
+        <v>1330.883666305314</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.9049234703619804</v>
+        <v>0.736886840792417</v>
       </c>
       <c r="C32">
-        <v>1.041681636072286</v>
+        <v>0.8487221460099431</v>
       </c>
       <c r="D32">
-        <v>0.0006988120195667371</v>
+        <v>0.0023696682464455</v>
       </c>
       <c r="E32">
-        <v>0.70013466432349</v>
+        <v>0.7029715218631571</v>
       </c>
       <c r="F32">
-        <v>6123.458000250968</v>
+        <v>9623.28174705128</v>
       </c>
       <c r="G32">
-        <v>7632.147130635087</v>
+        <v>11687.76161466941</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1333,22 +1333,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.9535457256018541</v>
+        <v>0.7113217099775129</v>
       </c>
       <c r="C33">
-        <v>1.184868294989723</v>
+        <v>0.8589481358715121</v>
       </c>
       <c r="D33">
-        <v>0.000713266761768899</v>
+        <v>0.002544529262086505</v>
       </c>
       <c r="E33">
-        <v>0.6920982455993094</v>
+        <v>0.6959008354590822</v>
       </c>
       <c r="F33">
-        <v>5460.627172271504</v>
+        <v>10904.52828633181</v>
       </c>
       <c r="G33">
-        <v>6635.045792813399</v>
+        <v>12865.49011207762</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.019854831984265</v>
+        <v>0.6802065453972648</v>
       </c>
       <c r="C34">
-        <v>1.244336291294026</v>
+        <v>0.7764315594395081</v>
       </c>
       <c r="D34">
-        <v>0.000730994152046781</v>
+        <v>0.002777777777777768</v>
       </c>
       <c r="E34">
-        <v>0.71497233248403</v>
+        <v>0.7181804809669858</v>
       </c>
       <c r="F34">
-        <v>5378.266989497894</v>
+        <v>14456.32738843468</v>
       </c>
       <c r="G34">
-        <v>6596.607872991262</v>
+        <v>17376.85254925521</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.019863312258381</v>
+        <v>0.6566481199221191</v>
       </c>
       <c r="C35">
-        <v>1.312986296750432</v>
+        <v>0.7763998634527414</v>
       </c>
       <c r="D35">
-        <v>0.000734214390602053</v>
+        <v>0.00283286118980169</v>
       </c>
       <c r="E35">
-        <v>0.7286110550287499</v>
+        <v>0.7324891618630752</v>
       </c>
       <c r="F35">
-        <v>4500.739217323573</v>
+        <v>14060.88790553151</v>
       </c>
       <c r="G35">
-        <v>5413.301273467368</v>
+        <v>16360.7820388286</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.027139916982323</v>
+        <v>0.6551639989051383</v>
       </c>
       <c r="C36">
-        <v>1.316703728187518</v>
+        <v>0.7570742392944146</v>
       </c>
       <c r="D36">
-        <v>0.00073691967575534</v>
+        <v>0.002873563218390795</v>
       </c>
       <c r="E36">
-        <v>0.7264119403618997</v>
+        <v>0.7304736748153263</v>
       </c>
       <c r="F36">
-        <v>3802.781843884292</v>
+        <v>12959.05706060579</v>
       </c>
       <c r="G36">
-        <v>4579.8531677764</v>
+        <v>15106.32848321054</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.8762255830828987</v>
+        <v>0.6781948623192956</v>
       </c>
       <c r="C37">
-        <v>0.976179704749904</v>
+        <v>0.7557034301558642</v>
       </c>
       <c r="D37">
-        <v>0.0007092198581560258</v>
+        <v>0.002481389578163763</v>
       </c>
       <c r="E37">
-        <v>0.7377110269737708</v>
+        <v>0.7372061701986623</v>
       </c>
       <c r="F37">
-        <v>7238.86083245517</v>
+        <v>11756.34439918427</v>
       </c>
       <c r="G37">
-        <v>7916.693079840804</v>
+        <v>12277.61144612404</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.027577622559291</v>
+        <v>0.6846017146411268</v>
       </c>
       <c r="C38">
-        <v>1.240714838713058</v>
+        <v>0.7726216946689727</v>
       </c>
       <c r="D38">
-        <v>0.000734214390602053</v>
+        <v>0.002785515320334252</v>
       </c>
       <c r="E38">
-        <v>0.7197222043785027</v>
+        <v>0.7202623884242696</v>
       </c>
       <c r="F38">
-        <v>6687.422831874392</v>
+        <v>14486.93918221869</v>
       </c>
       <c r="G38">
-        <v>7826.687995502895</v>
+        <v>16585.90919754051</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1513,22 +1513,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.5215189301546734</v>
+        <v>0.6824325418959341</v>
       </c>
       <c r="C39">
-        <v>0.5877699813908108</v>
+        <v>0.7598439720150727</v>
       </c>
       <c r="D39">
-        <v>0.002785515320334252</v>
+        <v>0.003003003003002993</v>
       </c>
       <c r="E39">
-        <v>0.7201330774030085</v>
+        <v>0.7145599096469799</v>
       </c>
       <c r="F39">
-        <v>12422.49192441842</v>
+        <v>16558.11155172021</v>
       </c>
       <c r="G39">
-        <v>13611.03443385328</v>
+        <v>19649.53885117804</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.5534747945606643</v>
+        <v>0.658778723076003</v>
       </c>
       <c r="C40">
-        <v>0.6179731711939276</v>
+        <v>0.7359986490055449</v>
       </c>
       <c r="D40">
-        <v>0.003012048192771073</v>
+        <v>0.003508771929824549</v>
       </c>
       <c r="E40">
-        <v>0.7134993799018865</v>
+        <v>0.7217047387325027</v>
       </c>
       <c r="F40">
-        <v>15767.92587679735</v>
+        <v>19516.47709665524</v>
       </c>
       <c r="G40">
-        <v>17913.65254074024</v>
+        <v>23398.16331538567</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.5600227321950216</v>
+        <v>0.5512327232302353</v>
       </c>
       <c r="C41">
-        <v>0.6379719877295922</v>
+        <v>0.5868856623665393</v>
       </c>
       <c r="D41">
-        <v>0.003546099290780129</v>
+        <v>0.007692307692307665</v>
       </c>
       <c r="E41">
-        <v>0.7178449057149298</v>
+        <v>0.7169432770638344</v>
       </c>
       <c r="F41">
-        <v>19621.23806605646</v>
+        <v>21207.63932174511</v>
       </c>
       <c r="G41">
-        <v>22380.76968647008</v>
+        <v>25078.42998510876</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1603,22 +1603,22 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.8922701130224272</v>
+        <v>0.7134406505264346</v>
       </c>
       <c r="C42">
-        <v>0.9979619707292152</v>
+        <v>0.799248723381678</v>
       </c>
       <c r="D42">
-        <v>0.0007022471910112366</v>
+        <v>0.002409638554216869</v>
       </c>
       <c r="E42">
-        <v>0.7204330360227654</v>
+        <v>0.7225210359168457</v>
       </c>
       <c r="F42">
-        <v>6737.899100096522</v>
+        <v>10846.11350518746</v>
       </c>
       <c r="G42">
-        <v>8131.312888958292</v>
+        <v>12622.98257650499</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.4856166948147464</v>
+        <v>0.6871910623288846</v>
       </c>
       <c r="C43">
-        <v>0.5430704102738293</v>
+        <v>0.8015858605684043</v>
       </c>
       <c r="D43">
-        <v>0.002409638554216869</v>
+        <v>0.002840909090909081</v>
       </c>
       <c r="E43">
-        <v>0.7223913193933418</v>
+        <v>0.7143821807716456</v>
       </c>
       <c r="F43">
-        <v>7393.587079901004</v>
+        <v>13930.85916346719</v>
       </c>
       <c r="G43">
-        <v>8110.232734417499</v>
+        <v>14734.69793514511</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.5236126791985455</v>
+        <v>0.6582978390153964</v>
       </c>
       <c r="C44">
-        <v>0.6097292969379284</v>
+        <v>0.7538547222873255</v>
       </c>
       <c r="D44">
         <v>0.002840909090909081</v>
       </c>
       <c r="E44">
-        <v>0.7142539254429613</v>
+        <v>0.7139115482460222</v>
       </c>
       <c r="F44">
-        <v>11962.75589099706</v>
+        <v>13968.58755480741</v>
       </c>
       <c r="G44">
-        <v>12132.81416305967</v>
+        <v>16654.1820505789</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.5332137771738227</v>
+        <v>0.6358525921130131</v>
       </c>
       <c r="C45">
-        <v>0.6099156990391607</v>
+        <v>0.7143531506955415</v>
       </c>
       <c r="D45">
-        <v>0.002840909090909081</v>
+        <v>0.003984063745019906</v>
       </c>
       <c r="E45">
-        <v>0.7137833774115077</v>
+        <v>0.7142572578734309</v>
       </c>
       <c r="F45">
-        <v>13326.06994153478</v>
+        <v>16204.60188063511</v>
       </c>
       <c r="G45">
-        <v>15236.09542572822</v>
+        <v>19572.14641796598</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1723,22 +1723,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.5389952811595231</v>
+        <v>0.6204771216272738</v>
       </c>
       <c r="C46">
-        <v>0.6047811784862009</v>
+        <v>0.6965926878202804</v>
       </c>
       <c r="D46">
         <v>0.003984063745019906</v>
       </c>
       <c r="E46">
-        <v>0.7141290249725558</v>
+        <v>0.7157880464469657</v>
       </c>
       <c r="F46">
-        <v>16343.67807830212</v>
+        <v>20013.00933808149</v>
       </c>
       <c r="G46">
-        <v>18974.46844145542</v>
+        <v>23618.55460364598</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1753,22 +1753,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.02734395492110341</v>
+        <v>0.1944555828724138</v>
       </c>
       <c r="C47">
-        <v>0.0301320142340732</v>
+        <v>0.1972060368705121</v>
       </c>
       <c r="D47">
-        <v>2.222466960352423</v>
+        <v>0.3129496402877697</v>
       </c>
       <c r="E47">
-        <v>0.9741233734636061</v>
+        <v>0.8996171603008141</v>
       </c>
       <c r="F47">
-        <v>1336.969108143822</v>
+        <v>314.9722688304263</v>
       </c>
       <c r="G47">
-        <v>1101.198676812705</v>
+        <v>152.3469528024018</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.1417458781056221</v>
+        <v>0.4199349726989943</v>
       </c>
       <c r="C48">
-        <v>0.1447682102021204</v>
+        <v>0.4440008878179534</v>
       </c>
       <c r="D48">
-        <v>0.3129496402877697</v>
+        <v>0.005681818181818161</v>
       </c>
       <c r="E48">
-        <v>0.8994556491409755</v>
+        <v>0.7306299642706362</v>
       </c>
       <c r="F48">
-        <v>863.6656619282259</v>
+        <v>3356.603885828662</v>
       </c>
       <c r="G48">
-        <v>641.7389664028875</v>
+        <v>2399.54328809959</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.3240328466672554</v>
+        <v>0.3244095495721811</v>
       </c>
       <c r="C49">
-        <v>0.3429738050797994</v>
+        <v>0.353522358727914</v>
       </c>
       <c r="D49">
         <v>0.005681818181818161</v>
       </c>
       <c r="E49">
-        <v>0.7304987919251658</v>
+        <v>0.7297262685431969</v>
       </c>
       <c r="F49">
-        <v>3220.549708798693</v>
+        <v>2241.649309419259</v>
       </c>
       <c r="G49">
-        <v>2283.006087107082</v>
+        <v>1602.181549796662</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1843,22 +1843,22 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.2646621464619882</v>
+        <v>0.3908722140598032</v>
       </c>
       <c r="C50">
-        <v>0.2882259820673069</v>
+        <v>0.422231254888875</v>
       </c>
       <c r="D50">
-        <v>0.005681818181818161</v>
+        <v>0.008849557522123862</v>
       </c>
       <c r="E50">
-        <v>0.7295952584411245</v>
+        <v>0.692745293040823</v>
       </c>
       <c r="F50">
-        <v>2418.992043162541</v>
+        <v>1885.588085949523</v>
       </c>
       <c r="G50">
-        <v>1714.43839135307</v>
+        <v>1336.099914482956</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.3294749126418805</v>
+        <v>0.3865922345321002</v>
       </c>
       <c r="C51">
-        <v>0.3557544732697349</v>
+        <v>0.4179480401624628</v>
       </c>
       <c r="D51">
-        <v>0.008849557522123862</v>
+        <v>0.009900990099009866</v>
       </c>
       <c r="E51">
-        <v>0.6926209222521263</v>
+        <v>0.6887244479945146</v>
       </c>
       <c r="F51">
-        <v>2137.880964596774</v>
+        <v>1530.789064268309</v>
       </c>
       <c r="G51">
-        <v>1500.356773161749</v>
+        <v>1082.575943689808</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.02734395492110341</v>
+        <v>0.1944555828724138</v>
       </c>
       <c r="C52">
-        <v>0.0301320142340732</v>
+        <v>0.1972060368705121</v>
       </c>
       <c r="D52">
-        <v>2.222466960352423</v>
+        <v>0.3129496402877697</v>
       </c>
       <c r="E52">
-        <v>0.9741233734636061</v>
+        <v>0.8996171603008141</v>
       </c>
       <c r="F52">
-        <v>1336.969108143822</v>
+        <v>314.9722688304263</v>
       </c>
       <c r="G52">
-        <v>1101.198676812705</v>
+        <v>152.3469528024018</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.1417458781056221</v>
+        <v>0.1280242504754841</v>
       </c>
       <c r="C53">
-        <v>0.1447682102021204</v>
+        <v>0.1544107498334182</v>
       </c>
       <c r="D53">
-        <v>0.3129496402877697</v>
+        <v>0.2446043165467625</v>
       </c>
       <c r="E53">
-        <v>0.8994556491409755</v>
+        <v>0.8816930288426401</v>
       </c>
       <c r="F53">
-        <v>863.6656619282259</v>
+        <v>158.9420820861596</v>
       </c>
       <c r="G53">
-        <v>641.7389664028875</v>
+        <v>77.42575655175156</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -1963,22 +1963,22 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.1026676759565925</v>
+        <v>0.1020427306378295</v>
       </c>
       <c r="C54">
-        <v>0.1232351628910585</v>
+        <v>0.1095776443357989</v>
       </c>
       <c r="D54">
-        <v>0.2446043165467625</v>
+        <v>0.07553956834532378</v>
       </c>
       <c r="E54">
-        <v>0.881534735659724</v>
+        <v>0.8814317213521734</v>
       </c>
       <c r="F54">
-        <v>576.9007656553219</v>
+        <v>105.995479033884</v>
       </c>
       <c r="G54">
-        <v>428.7600180454888</v>
+        <v>51.6884135543381</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.08695377499024713</v>
+        <v>0.1191798362625988</v>
       </c>
       <c r="C55">
-        <v>0.09360379588143498</v>
+        <v>0.1266204370581611</v>
       </c>
       <c r="D55">
-        <v>0.07553956834532378</v>
+        <v>0.06923076923076926</v>
       </c>
       <c r="E55">
-        <v>0.8812734750826309</v>
+        <v>0.8335933526060766</v>
       </c>
       <c r="F55">
-        <v>432.6472526857038</v>
+        <v>91.10913477934641</v>
       </c>
       <c r="G55">
-        <v>321.5845696081233</v>
+        <v>49.03671481099833</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.1037323573996905</v>
+        <v>0.1647335323754312</v>
       </c>
       <c r="C56">
-        <v>0.110451174069675</v>
+        <v>0.1682158060800221</v>
       </c>
       <c r="D56">
-        <v>0.06923076923076926</v>
+        <v>0.03404255319148939</v>
       </c>
       <c r="E56">
-        <v>0.8334436949126105</v>
+        <v>0.8138553566622707</v>
       </c>
       <c r="F56">
-        <v>357.5904871478671</v>
+        <v>112.0180261020748</v>
       </c>
       <c r="G56">
-        <v>267.0693897958657</v>
+        <v>74.25386650182591</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2053,22 +2053,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.02734395492110341</v>
+        <v>0.1944555828724138</v>
       </c>
       <c r="C57">
-        <v>0.0301320142340732</v>
+        <v>0.1972060368705121</v>
       </c>
       <c r="D57">
-        <v>2.222466960352423</v>
+        <v>0.3129496402877697</v>
       </c>
       <c r="E57">
-        <v>0.9741233734636061</v>
+        <v>0.8996171603008141</v>
       </c>
       <c r="F57">
-        <v>1336.969108143822</v>
+        <v>314.9722688304263</v>
       </c>
       <c r="G57">
-        <v>1101.198676812705</v>
+        <v>152.3469528024018</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2083,22 +2083,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.1417458781056221</v>
+        <v>0.4141160518221578</v>
       </c>
       <c r="C58">
-        <v>0.1447682102021204</v>
+        <v>0.4270916605904978</v>
       </c>
       <c r="D58">
-        <v>0.3129496402877697</v>
+        <v>0.005882352941176554</v>
       </c>
       <c r="E58">
-        <v>0.8994556491409755</v>
+        <v>0.7310380474646212</v>
       </c>
       <c r="F58">
-        <v>863.6656619282259</v>
+        <v>2999.652668049377</v>
       </c>
       <c r="G58">
-        <v>641.7389664028875</v>
+        <v>2093.345443730012</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2113,22 +2113,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.3196686560096281</v>
+        <v>0.4494502312709366</v>
       </c>
       <c r="C59">
-        <v>0.3302918846592076</v>
+        <v>0.4576044455780459</v>
       </c>
       <c r="D59">
-        <v>0.005882352941176554</v>
+        <v>0.009345794392523497</v>
       </c>
       <c r="E59">
-        <v>0.7309068018546634</v>
+        <v>0.7003044013913833</v>
       </c>
       <c r="F59">
-        <v>2925.442293583142</v>
+        <v>2201.283027972432</v>
       </c>
       <c r="G59">
-        <v>2038.502464200893</v>
+        <v>1519.520657862692</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.366825478731157</v>
+        <v>0.4964152368348642</v>
       </c>
       <c r="C60">
-        <v>0.3740620678355041</v>
+        <v>0.5170670019461072</v>
       </c>
       <c r="D60">
-        <v>0.009345794392523497</v>
+        <v>0.01052631578947374</v>
       </c>
       <c r="E60">
-        <v>0.7001786734916721</v>
+        <v>0.6871361893500151</v>
       </c>
       <c r="F60">
-        <v>2381.447872041719</v>
+        <v>7647.375165542444</v>
       </c>
       <c r="G60">
-        <v>1640.181668412582</v>
+        <v>6785.959553568397</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2173,22 +2173,22 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.4197337754577266</v>
+        <v>0.5030900087191345</v>
       </c>
       <c r="C61">
-        <v>0.4375379277659789</v>
+        <v>0.5242080735752424</v>
       </c>
       <c r="D61">
-        <v>0.01052631578947374</v>
+        <v>0.01123595505617984</v>
       </c>
       <c r="E61">
-        <v>0.6870128255817296</v>
+        <v>0.6852201477110609</v>
       </c>
       <c r="F61">
-        <v>7854.111107167368</v>
+        <v>6190.801521584344</v>
       </c>
       <c r="G61">
-        <v>6722.511470547322</v>
+        <v>5474.545469076982</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>

--- a/databases/metricas_avaliacao_clusters.xlsx
+++ b/databases/metricas_avaliacao_clusters.xlsx
@@ -403,22 +403,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7921386638930618</v>
+        <v>0.7921</v>
       </c>
       <c r="C2">
-        <v>0.9656836697298948</v>
+        <v>0.9657</v>
       </c>
       <c r="D2">
-        <v>0.001594896331738431</v>
+        <v>0.0016</v>
       </c>
       <c r="E2">
-        <v>0.6962785504213564</v>
+        <v>0.6963</v>
       </c>
       <c r="F2">
-        <v>8109.234314366015</v>
+        <v>8109.2343</v>
       </c>
       <c r="G2">
-        <v>9695.03555022506</v>
+        <v>9695.035599999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -433,22 +433,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.7409590842431715</v>
+        <v>0.741</v>
       </c>
       <c r="C3">
-        <v>0.8473853207615423</v>
+        <v>0.8474</v>
       </c>
       <c r="D3">
-        <v>0.001715265866209264</v>
+        <v>0.0017</v>
       </c>
       <c r="E3">
-        <v>0.7115145972499541</v>
+        <v>0.7115</v>
       </c>
       <c r="F3">
-        <v>10382.20471462729</v>
+        <v>10382.2047</v>
       </c>
       <c r="G3">
-        <v>12675.40697608507</v>
+        <v>12675.407</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -463,22 +463,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.7332471668662663</v>
+        <v>0.7332</v>
       </c>
       <c r="C4">
-        <v>0.860316877404434</v>
+        <v>0.8603</v>
       </c>
       <c r="D4">
-        <v>0.001766784452296813</v>
+        <v>0.0018</v>
       </c>
       <c r="E4">
-        <v>0.7090514933228995</v>
+        <v>0.7091</v>
       </c>
       <c r="F4">
-        <v>9782.009177852766</v>
+        <v>9782.0092</v>
       </c>
       <c r="G4">
-        <v>11721.80198026232</v>
+        <v>11721.802</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7424733057440944</v>
+        <v>0.7425</v>
       </c>
       <c r="C5">
-        <v>0.9341181358009374</v>
+        <v>0.9341</v>
       </c>
       <c r="D5">
-        <v>0.00181488203266787</v>
+        <v>0.0018</v>
       </c>
       <c r="E5">
-        <v>0.7168033615433581</v>
+        <v>0.7168</v>
       </c>
       <c r="F5">
-        <v>9412.567879535103</v>
+        <v>9412.5679</v>
       </c>
       <c r="G5">
-        <v>10991.33537419847</v>
+        <v>10991.3354</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.7290653489051589</v>
+        <v>0.7291</v>
       </c>
       <c r="C6">
-        <v>0.9108856787515828</v>
+        <v>0.9109</v>
       </c>
       <c r="D6">
-        <v>0.001834862385321094</v>
+        <v>0.0018</v>
       </c>
       <c r="E6">
-        <v>0.7236426044474198</v>
+        <v>0.7236</v>
       </c>
       <c r="F6">
-        <v>8411.112067538839</v>
+        <v>8411.1121</v>
       </c>
       <c r="G6">
-        <v>9781.47507323989</v>
+        <v>9781.4751</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7183591274932485</v>
+        <v>0.7184</v>
       </c>
       <c r="C7">
-        <v>0.7860424993761649</v>
+        <v>0.786</v>
       </c>
       <c r="D7">
-        <v>0.001666666666666661</v>
+        <v>0.0017</v>
       </c>
       <c r="E7">
-        <v>0.7420273857319543</v>
+        <v>0.742</v>
       </c>
       <c r="F7">
-        <v>10316.50312925316</v>
+        <v>10316.5031</v>
       </c>
       <c r="G7">
-        <v>10741.80402207091</v>
+        <v>10741.804</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.7505295310804454</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="C8">
-        <v>0.8734997492287507</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="D8">
-        <v>0.001795332136445244</v>
+        <v>0.0018</v>
       </c>
       <c r="E8">
-        <v>0.7199106460213437</v>
+        <v>0.7199</v>
       </c>
       <c r="F8">
-        <v>11727.42992223991</v>
+        <v>11727.4299</v>
       </c>
       <c r="G8">
-        <v>13361.27192016878</v>
+        <v>13361.2719</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.7615978523819178</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="C9">
-        <v>0.942774051430089</v>
+        <v>0.9428</v>
       </c>
       <c r="D9">
-        <v>0.002004008016032066</v>
+        <v>0.002</v>
       </c>
       <c r="E9">
-        <v>0.7216899676452846</v>
+        <v>0.7217</v>
       </c>
       <c r="F9">
-        <v>13023.63781900941</v>
+        <v>13023.6378</v>
       </c>
       <c r="G9">
-        <v>15141.52070482313</v>
+        <v>15141.5207</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.5825913203616401</v>
+        <v>0.5826</v>
       </c>
       <c r="C10">
-        <v>0.6376043147213164</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="D10">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E10">
-        <v>0.7204560891611551</v>
+        <v>0.7205</v>
       </c>
       <c r="F10">
-        <v>16587.42630116144</v>
+        <v>16587.4263</v>
       </c>
       <c r="G10">
-        <v>19198.94995451903</v>
+        <v>19198.95</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.5825055690645841</v>
+        <v>0.5825</v>
       </c>
       <c r="C11">
-        <v>0.6536829015094212</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="D11">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E11">
-        <v>0.7182137294561327</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F11">
-        <v>20636.97660213238</v>
+        <v>20636.9766</v>
       </c>
       <c r="G11">
-        <v>23805.65466837364</v>
+        <v>23805.6547</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.7053803477032572</v>
+        <v>0.7054</v>
       </c>
       <c r="C12">
-        <v>0.7564631773331069</v>
+        <v>0.7565</v>
       </c>
       <c r="D12">
-        <v>0.001680672268907557</v>
+        <v>0.0017</v>
       </c>
       <c r="E12">
-        <v>0.7449461241127394</v>
+        <v>0.7449</v>
       </c>
       <c r="F12">
-        <v>10246.45050768732</v>
+        <v>10246.4505</v>
       </c>
       <c r="G12">
-        <v>10367.36273918394</v>
+        <v>10367.3627</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -733,22 +733,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.7800664596414588</v>
+        <v>0.7801</v>
       </c>
       <c r="C13">
-        <v>0.9363643663653314</v>
+        <v>0.9364</v>
       </c>
       <c r="D13">
-        <v>0.001680672268907557</v>
+        <v>0.0017</v>
       </c>
       <c r="E13">
-        <v>0.6883586903922368</v>
+        <v>0.6884</v>
       </c>
       <c r="F13">
-        <v>8985.697260377401</v>
+        <v>8985.6973</v>
       </c>
       <c r="G13">
-        <v>10897.55806299406</v>
+        <v>10897.5581</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.7506189534028507</v>
+        <v>0.7506</v>
       </c>
       <c r="C14">
-        <v>0.9191916800215086</v>
+        <v>0.9192</v>
       </c>
       <c r="D14">
-        <v>0.001953124999999993</v>
+        <v>0.002</v>
       </c>
       <c r="E14">
-        <v>0.7100629162544673</v>
+        <v>0.7101</v>
       </c>
       <c r="F14">
-        <v>12473.90242804929</v>
+        <v>12473.9024</v>
       </c>
       <c r="G14">
-        <v>14311.13603291362</v>
+        <v>14311.136</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.5656024372176113</v>
+        <v>0.5656</v>
       </c>
       <c r="C15">
-        <v>0.6257846277592742</v>
+        <v>0.6258</v>
       </c>
       <c r="D15">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E15">
-        <v>0.7100889731900483</v>
+        <v>0.7101</v>
       </c>
       <c r="F15">
-        <v>15662.34535734599</v>
+        <v>15662.3454</v>
       </c>
       <c r="G15">
-        <v>17904.07075757172</v>
+        <v>17904.0708</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.5928858433194888</v>
+        <v>0.5929</v>
       </c>
       <c r="C16">
-        <v>0.6724545072721113</v>
+        <v>0.6725</v>
       </c>
       <c r="D16">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E16">
-        <v>0.7105629453110597</v>
+        <v>0.7106</v>
       </c>
       <c r="F16">
-        <v>18337.79243504147</v>
+        <v>18337.7924</v>
       </c>
       <c r="G16">
-        <v>20465.34502241612</v>
+        <v>20465.345</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -853,22 +853,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.09788433563054418</v>
+        <v>0.0979</v>
       </c>
       <c r="C17">
-        <v>0.1171797793816212</v>
+        <v>0.1172</v>
       </c>
       <c r="D17">
-        <v>0.3130252100840336</v>
+        <v>0.313</v>
       </c>
       <c r="E17">
-        <v>0.9322552304793569</v>
+        <v>0.9323</v>
       </c>
       <c r="F17">
-        <v>414.6981733148527</v>
+        <v>414.6982</v>
       </c>
       <c r="G17">
-        <v>354.5385277928403</v>
+        <v>354.5385</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -883,22 +883,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.2146482440885665</v>
+        <v>0.2146</v>
       </c>
       <c r="C18">
-        <v>0.2649332763876824</v>
+        <v>0.2649</v>
       </c>
       <c r="D18">
-        <v>0.3151125401929259</v>
+        <v>0.3151</v>
       </c>
       <c r="E18">
-        <v>0.8938425208602352</v>
+        <v>0.8938</v>
       </c>
       <c r="F18">
-        <v>359.0953714209782</v>
+        <v>359.0954</v>
       </c>
       <c r="G18">
-        <v>309.1030665340019</v>
+        <v>309.1031</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.1077026866909191</v>
+        <v>0.1077</v>
       </c>
       <c r="C19">
-        <v>0.1419581126004041</v>
+        <v>0.142</v>
       </c>
       <c r="D19">
-        <v>0.2122186495176849</v>
+        <v>0.2122</v>
       </c>
       <c r="E19">
-        <v>0.8867424995401773</v>
+        <v>0.8867</v>
       </c>
       <c r="F19">
-        <v>239.9931130639536</v>
+        <v>239.9931</v>
       </c>
       <c r="G19">
-        <v>206.7695911977547</v>
+        <v>206.7696</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.08979748823712735</v>
+        <v>0.0898</v>
       </c>
       <c r="C20">
-        <v>0.09641883286624867</v>
+        <v>0.0964</v>
       </c>
       <c r="D20">
-        <v>0.112540192926045</v>
+        <v>0.1125</v>
       </c>
       <c r="E20">
-        <v>0.886459704912805</v>
+        <v>0.8865</v>
       </c>
       <c r="F20">
-        <v>180.0621093224045</v>
+        <v>180.0621</v>
       </c>
       <c r="G20">
-        <v>155.2050058160424</v>
+        <v>155.205</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.1111660533155121</v>
+        <v>0.1112</v>
       </c>
       <c r="C21">
-        <v>0.1174147798005934</v>
+        <v>0.1174</v>
       </c>
       <c r="D21">
-        <v>0.04912280701754381</v>
+        <v>0.0491</v>
       </c>
       <c r="E21">
-        <v>0.838298757762344</v>
+        <v>0.8383</v>
       </c>
       <c r="F21">
-        <v>175.1997006219439</v>
+        <v>175.1997</v>
       </c>
       <c r="G21">
-        <v>152.2744222528795</v>
+        <v>152.2744</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.3035014612166439</v>
+        <v>0.3035</v>
       </c>
       <c r="C22">
-        <v>0.3418961777605273</v>
+        <v>0.3419</v>
       </c>
       <c r="D22">
-        <v>0.3151125401929259</v>
+        <v>0.3151</v>
       </c>
       <c r="E22">
-        <v>0.914049344840546</v>
+        <v>0.914</v>
       </c>
       <c r="F22">
-        <v>683.8129655465774</v>
+        <v>683.813</v>
       </c>
       <c r="G22">
-        <v>588.3170937312703</v>
+        <v>588.3171</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.4413146668735033</v>
+        <v>0.4413</v>
       </c>
       <c r="C23">
-        <v>0.5099334292151916</v>
+        <v>0.5099</v>
       </c>
       <c r="D23">
-        <v>0.0199203187250996</v>
+        <v>0.0199</v>
       </c>
       <c r="E23">
-        <v>0.7896402423141253</v>
+        <v>0.7896</v>
       </c>
       <c r="F23">
-        <v>865.034424258139</v>
+        <v>865.0344</v>
       </c>
       <c r="G23">
-        <v>782.7477138605682</v>
+        <v>782.7477</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.3035036705526018</v>
+        <v>0.3035</v>
       </c>
       <c r="C24">
-        <v>0.353742100141515</v>
+        <v>0.3537</v>
       </c>
       <c r="D24">
-        <v>0.02512562814070352</v>
+        <v>0.0251</v>
       </c>
       <c r="E24">
-        <v>0.7897301568202093</v>
+        <v>0.7897</v>
       </c>
       <c r="F24">
-        <v>592.2712032302167</v>
+        <v>592.2712</v>
       </c>
       <c r="G24">
-        <v>535.1718334699847</v>
+        <v>535.1718</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1093,22 +1093,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.417301610174766</v>
+        <v>0.4173</v>
       </c>
       <c r="C25">
-        <v>0.449286915172545</v>
+        <v>0.4493</v>
       </c>
       <c r="D25">
-        <v>0.007874015748031539</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="E25">
-        <v>0.7280126377645855</v>
+        <v>0.728</v>
       </c>
       <c r="F25">
-        <v>4483.106811983894</v>
+        <v>4483.1068</v>
       </c>
       <c r="G25">
-        <v>3915.764066549737</v>
+        <v>3915.7641</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4741782697889286</v>
+        <v>0.4742</v>
       </c>
       <c r="C26">
-        <v>0.5156359733455057</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="D26">
-        <v>0.009345794392523412</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E26">
-        <v>0.6908633954396576</v>
+        <v>0.6909</v>
       </c>
       <c r="F26">
-        <v>4507.767724189112</v>
+        <v>4507.7677</v>
       </c>
       <c r="G26">
-        <v>3735.380668741548</v>
+        <v>3735.3807</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.4220732461249934</v>
+        <v>0.4221</v>
       </c>
       <c r="C27">
-        <v>0.4498079282799691</v>
+        <v>0.4498</v>
       </c>
       <c r="D27">
-        <v>0.038781163434903</v>
+        <v>0.0388</v>
       </c>
       <c r="E27">
-        <v>0.8962282144145611</v>
+        <v>0.8962</v>
       </c>
       <c r="F27">
-        <v>782.7634117339105</v>
+        <v>782.7634</v>
       </c>
       <c r="G27">
-        <v>685.3112220795941</v>
+        <v>685.3112</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.3125424208524248</v>
+        <v>0.3125</v>
       </c>
       <c r="C28">
-        <v>0.4185968610906735</v>
+        <v>0.4186</v>
       </c>
       <c r="D28">
-        <v>0.04912280701754381</v>
+        <v>0.0491</v>
       </c>
       <c r="E28">
-        <v>0.8723621734205375</v>
+        <v>0.8724</v>
       </c>
       <c r="F28">
-        <v>428.9921101569612</v>
+        <v>428.9921</v>
       </c>
       <c r="G28">
-        <v>370.997349530146</v>
+        <v>370.9973</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1213,22 +1213,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.4332066054843731</v>
+        <v>0.4332</v>
       </c>
       <c r="C29">
-        <v>0.4960995890416366</v>
+        <v>0.4961</v>
       </c>
       <c r="D29">
-        <v>0.005649717514124273</v>
+        <v>0.0056</v>
       </c>
       <c r="E29">
-        <v>0.7333631821407731</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="F29">
-        <v>2727.72603995589</v>
+        <v>2727.726</v>
       </c>
       <c r="G29">
-        <v>2014.473508603711</v>
+        <v>2014.4735</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.3567137252070376</v>
+        <v>0.3567</v>
       </c>
       <c r="C30">
-        <v>0.4399384965470529</v>
+        <v>0.4399</v>
       </c>
       <c r="D30">
-        <v>0.005747126436781589</v>
+        <v>0.0057</v>
       </c>
       <c r="E30">
-        <v>0.7308181288333772</v>
+        <v>0.7308</v>
       </c>
       <c r="F30">
-        <v>2063.861669336371</v>
+        <v>2063.8617</v>
       </c>
       <c r="G30">
-        <v>1524.856654985365</v>
+        <v>1524.8567</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4127182840288467</v>
+        <v>0.4127</v>
       </c>
       <c r="C31">
-        <v>0.4955497421433226</v>
+        <v>0.4955</v>
       </c>
       <c r="D31">
-        <v>0.009090909090909059</v>
+        <v>0.0091</v>
       </c>
       <c r="E31">
-        <v>0.697028718967043</v>
+        <v>0.697</v>
       </c>
       <c r="F31">
-        <v>1822.9624769826</v>
+        <v>1822.9625</v>
       </c>
       <c r="G31">
-        <v>1330.883666305314</v>
+        <v>1330.8837</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.736886840792417</v>
+        <v>0.7369</v>
       </c>
       <c r="C32">
-        <v>0.8487221460099431</v>
+        <v>0.8487</v>
       </c>
       <c r="D32">
-        <v>0.0023696682464455</v>
+        <v>0.0024</v>
       </c>
       <c r="E32">
-        <v>0.7029715218631571</v>
+        <v>0.703</v>
       </c>
       <c r="F32">
-        <v>9623.28174705128</v>
+        <v>9623.2817</v>
       </c>
       <c r="G32">
-        <v>11687.76161466941</v>
+        <v>11687.7616</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1333,22 +1333,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.7113217099775129</v>
+        <v>0.7113</v>
       </c>
       <c r="C33">
-        <v>0.8589481358715121</v>
+        <v>0.8589</v>
       </c>
       <c r="D33">
-        <v>0.002544529262086505</v>
+        <v>0.0025</v>
       </c>
       <c r="E33">
-        <v>0.6959008354590822</v>
+        <v>0.6959</v>
       </c>
       <c r="F33">
-        <v>10904.52828633181</v>
+        <v>10904.5283</v>
       </c>
       <c r="G33">
-        <v>12865.49011207762</v>
+        <v>12865.4901</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.6802065453972648</v>
+        <v>0.6802</v>
       </c>
       <c r="C34">
-        <v>0.7764315594395081</v>
+        <v>0.7764</v>
       </c>
       <c r="D34">
-        <v>0.002777777777777768</v>
+        <v>0.0028</v>
       </c>
       <c r="E34">
-        <v>0.7181804809669858</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F34">
-        <v>14456.32738843468</v>
+        <v>14456.3274</v>
       </c>
       <c r="G34">
-        <v>17376.85254925521</v>
+        <v>17376.8525</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.6566481199221191</v>
+        <v>0.6566</v>
       </c>
       <c r="C35">
-        <v>0.7763998634527414</v>
+        <v>0.7764</v>
       </c>
       <c r="D35">
-        <v>0.00283286118980169</v>
+        <v>0.0028</v>
       </c>
       <c r="E35">
-        <v>0.7324891618630752</v>
+        <v>0.7325</v>
       </c>
       <c r="F35">
-        <v>14060.88790553151</v>
+        <v>14060.8879</v>
       </c>
       <c r="G35">
-        <v>16360.7820388286</v>
+        <v>16360.782</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.6551639989051383</v>
+        <v>0.6552</v>
       </c>
       <c r="C36">
-        <v>0.7570742392944146</v>
+        <v>0.7571</v>
       </c>
       <c r="D36">
-        <v>0.002873563218390795</v>
+        <v>0.0029</v>
       </c>
       <c r="E36">
-        <v>0.7304736748153263</v>
+        <v>0.7305</v>
       </c>
       <c r="F36">
-        <v>12959.05706060579</v>
+        <v>12959.0571</v>
       </c>
       <c r="G36">
-        <v>15106.32848321054</v>
+        <v>15106.3285</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6781948623192956</v>
+        <v>0.6782</v>
       </c>
       <c r="C37">
-        <v>0.7557034301558642</v>
+        <v>0.7557</v>
       </c>
       <c r="D37">
-        <v>0.002481389578163763</v>
+        <v>0.0025</v>
       </c>
       <c r="E37">
-        <v>0.7372061701986623</v>
+        <v>0.7372</v>
       </c>
       <c r="F37">
-        <v>11756.34439918427</v>
+        <v>11756.3444</v>
       </c>
       <c r="G37">
-        <v>12277.61144612404</v>
+        <v>12277.6114</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.6846017146411268</v>
+        <v>0.6846</v>
       </c>
       <c r="C38">
-        <v>0.7726216946689727</v>
+        <v>0.7726</v>
       </c>
       <c r="D38">
-        <v>0.002785515320334252</v>
+        <v>0.0028</v>
       </c>
       <c r="E38">
-        <v>0.7202623884242696</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="F38">
-        <v>14486.93918221869</v>
+        <v>14486.9392</v>
       </c>
       <c r="G38">
-        <v>16585.90919754051</v>
+        <v>16585.9092</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1513,22 +1513,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.6824325418959341</v>
+        <v>0.6824</v>
       </c>
       <c r="C39">
-        <v>0.7598439720150727</v>
+        <v>0.7598</v>
       </c>
       <c r="D39">
-        <v>0.003003003003002993</v>
+        <v>0.003</v>
       </c>
       <c r="E39">
-        <v>0.7145599096469799</v>
+        <v>0.7146</v>
       </c>
       <c r="F39">
-        <v>16558.11155172021</v>
+        <v>16558.1116</v>
       </c>
       <c r="G39">
-        <v>19649.53885117804</v>
+        <v>19649.5389</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.658778723076003</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="C40">
-        <v>0.7359986490055449</v>
+        <v>0.736</v>
       </c>
       <c r="D40">
-        <v>0.003508771929824549</v>
+        <v>0.0035</v>
       </c>
       <c r="E40">
-        <v>0.7217047387325027</v>
+        <v>0.7217</v>
       </c>
       <c r="F40">
-        <v>19516.47709665524</v>
+        <v>19516.4771</v>
       </c>
       <c r="G40">
-        <v>23398.16331538567</v>
+        <v>23398.1633</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.5512327232302353</v>
+        <v>0.5512</v>
       </c>
       <c r="C41">
-        <v>0.5868856623665393</v>
+        <v>0.5869</v>
       </c>
       <c r="D41">
-        <v>0.007692307692307665</v>
+        <v>0.0077</v>
       </c>
       <c r="E41">
-        <v>0.7169432770638344</v>
+        <v>0.7169</v>
       </c>
       <c r="F41">
-        <v>21207.63932174511</v>
+        <v>21207.6393</v>
       </c>
       <c r="G41">
-        <v>25078.42998510876</v>
+        <v>25078.43</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1603,22 +1603,22 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.7134406505264346</v>
+        <v>0.7134</v>
       </c>
       <c r="C42">
-        <v>0.799248723381678</v>
+        <v>0.7992</v>
       </c>
       <c r="D42">
-        <v>0.002409638554216869</v>
+        <v>0.0024</v>
       </c>
       <c r="E42">
-        <v>0.7225210359168457</v>
+        <v>0.7225</v>
       </c>
       <c r="F42">
-        <v>10846.11350518746</v>
+        <v>10846.1135</v>
       </c>
       <c r="G42">
-        <v>12622.98257650499</v>
+        <v>12622.9826</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.6871910623288846</v>
+        <v>0.6872</v>
       </c>
       <c r="C43">
-        <v>0.8015858605684043</v>
+        <v>0.8016</v>
       </c>
       <c r="D43">
-        <v>0.002840909090909081</v>
+        <v>0.0028</v>
       </c>
       <c r="E43">
-        <v>0.7143821807716456</v>
+        <v>0.7144</v>
       </c>
       <c r="F43">
-        <v>13930.85916346719</v>
+        <v>13930.8592</v>
       </c>
       <c r="G43">
-        <v>14734.69793514511</v>
+        <v>14734.6979</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.6582978390153964</v>
+        <v>0.6583</v>
       </c>
       <c r="C44">
-        <v>0.7538547222873255</v>
+        <v>0.7539</v>
       </c>
       <c r="D44">
-        <v>0.002840909090909081</v>
+        <v>0.0028</v>
       </c>
       <c r="E44">
-        <v>0.7139115482460222</v>
+        <v>0.7139</v>
       </c>
       <c r="F44">
-        <v>13968.58755480741</v>
+        <v>13968.5876</v>
       </c>
       <c r="G44">
-        <v>16654.1820505789</v>
+        <v>16654.1821</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.6358525921130131</v>
+        <v>0.6359</v>
       </c>
       <c r="C45">
-        <v>0.7143531506955415</v>
+        <v>0.7144</v>
       </c>
       <c r="D45">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E45">
-        <v>0.7142572578734309</v>
+        <v>0.7143</v>
       </c>
       <c r="F45">
-        <v>16204.60188063511</v>
+        <v>16204.6019</v>
       </c>
       <c r="G45">
-        <v>19572.14641796598</v>
+        <v>19572.1464</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1723,22 +1723,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.6204771216272738</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="C46">
-        <v>0.6965926878202804</v>
+        <v>0.6966</v>
       </c>
       <c r="D46">
-        <v>0.003984063745019906</v>
+        <v>0.004</v>
       </c>
       <c r="E46">
-        <v>0.7157880464469657</v>
+        <v>0.7158</v>
       </c>
       <c r="F46">
-        <v>20013.00933808149</v>
+        <v>20013.0093</v>
       </c>
       <c r="G46">
-        <v>23618.55460364598</v>
+        <v>23618.5546</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1753,22 +1753,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.1944555828724138</v>
+        <v>0.1945</v>
       </c>
       <c r="C47">
-        <v>0.1972060368705121</v>
+        <v>0.1972</v>
       </c>
       <c r="D47">
-        <v>0.3129496402877697</v>
+        <v>0.3129</v>
       </c>
       <c r="E47">
-        <v>0.8996171603008141</v>
+        <v>0.8996</v>
       </c>
       <c r="F47">
-        <v>314.9722688304263</v>
+        <v>314.9723</v>
       </c>
       <c r="G47">
-        <v>152.3469528024018</v>
+        <v>152.347</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.4199349726989943</v>
+        <v>0.4199</v>
       </c>
       <c r="C48">
-        <v>0.4440008878179534</v>
+        <v>0.444</v>
       </c>
       <c r="D48">
-        <v>0.005681818181818161</v>
+        <v>0.0057</v>
       </c>
       <c r="E48">
-        <v>0.7306299642706362</v>
+        <v>0.7306</v>
       </c>
       <c r="F48">
-        <v>3356.603885828662</v>
+        <v>3356.6039</v>
       </c>
       <c r="G48">
-        <v>2399.54328809959</v>
+        <v>2399.5433</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.3244095495721811</v>
+        <v>0.3244</v>
       </c>
       <c r="C49">
-        <v>0.353522358727914</v>
+        <v>0.3535</v>
       </c>
       <c r="D49">
-        <v>0.005681818181818161</v>
+        <v>0.0057</v>
       </c>
       <c r="E49">
-        <v>0.7297262685431969</v>
+        <v>0.7297</v>
       </c>
       <c r="F49">
-        <v>2241.649309419259</v>
+        <v>2241.6493</v>
       </c>
       <c r="G49">
-        <v>1602.181549796662</v>
+        <v>1602.1815</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1843,22 +1843,22 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.3908722140598032</v>
+        <v>0.3909</v>
       </c>
       <c r="C50">
-        <v>0.422231254888875</v>
+        <v>0.4222</v>
       </c>
       <c r="D50">
-        <v>0.008849557522123862</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E50">
-        <v>0.692745293040823</v>
+        <v>0.6927</v>
       </c>
       <c r="F50">
-        <v>1885.588085949523</v>
+        <v>1885.5881</v>
       </c>
       <c r="G50">
-        <v>1336.099914482956</v>
+        <v>1336.0999</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.3865922345321002</v>
+        <v>0.3866</v>
       </c>
       <c r="C51">
-        <v>0.4179480401624628</v>
+        <v>0.4179</v>
       </c>
       <c r="D51">
-        <v>0.009900990099009866</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E51">
-        <v>0.6887244479945146</v>
+        <v>0.6887</v>
       </c>
       <c r="F51">
-        <v>1530.789064268309</v>
+        <v>1530.7891</v>
       </c>
       <c r="G51">
-        <v>1082.575943689808</v>
+        <v>1082.5759</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.1944555828724138</v>
+        <v>0.1945</v>
       </c>
       <c r="C52">
-        <v>0.1972060368705121</v>
+        <v>0.1972</v>
       </c>
       <c r="D52">
-        <v>0.3129496402877697</v>
+        <v>0.3129</v>
       </c>
       <c r="E52">
-        <v>0.8996171603008141</v>
+        <v>0.8996</v>
       </c>
       <c r="F52">
-        <v>314.9722688304263</v>
+        <v>314.9723</v>
       </c>
       <c r="G52">
-        <v>152.3469528024018</v>
+        <v>152.347</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.1280242504754841</v>
+        <v>0.128</v>
       </c>
       <c r="C53">
-        <v>0.1544107498334182</v>
+        <v>0.1544</v>
       </c>
       <c r="D53">
-        <v>0.2446043165467625</v>
+        <v>0.2446</v>
       </c>
       <c r="E53">
-        <v>0.8816930288426401</v>
+        <v>0.8817</v>
       </c>
       <c r="F53">
-        <v>158.9420820861596</v>
+        <v>158.9421</v>
       </c>
       <c r="G53">
-        <v>77.42575655175156</v>
+        <v>77.4258</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -1963,22 +1963,22 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.1020427306378295</v>
+        <v>0.102</v>
       </c>
       <c r="C54">
-        <v>0.1095776443357989</v>
+        <v>0.1096</v>
       </c>
       <c r="D54">
-        <v>0.07553956834532378</v>
+        <v>0.0755</v>
       </c>
       <c r="E54">
-        <v>0.8814317213521734</v>
+        <v>0.8814</v>
       </c>
       <c r="F54">
-        <v>105.995479033884</v>
+        <v>105.9955</v>
       </c>
       <c r="G54">
-        <v>51.6884135543381</v>
+        <v>51.6884</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.1191798362625988</v>
+        <v>0.1192</v>
       </c>
       <c r="C55">
-        <v>0.1266204370581611</v>
+        <v>0.1266</v>
       </c>
       <c r="D55">
-        <v>0.06923076923076926</v>
+        <v>0.0692</v>
       </c>
       <c r="E55">
-        <v>0.8335933526060766</v>
+        <v>0.8336</v>
       </c>
       <c r="F55">
-        <v>91.10913477934641</v>
+        <v>91.1091</v>
       </c>
       <c r="G55">
-        <v>49.03671481099833</v>
+        <v>49.0367</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.1647335323754312</v>
+        <v>0.1647</v>
       </c>
       <c r="C56">
-        <v>0.1682158060800221</v>
+        <v>0.1682</v>
       </c>
       <c r="D56">
-        <v>0.03404255319148939</v>
+        <v>0.034</v>
       </c>
       <c r="E56">
-        <v>0.8138553566622707</v>
+        <v>0.8139</v>
       </c>
       <c r="F56">
-        <v>112.0180261020748</v>
+        <v>112.018</v>
       </c>
       <c r="G56">
-        <v>74.25386650182591</v>
+        <v>74.2539</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2053,22 +2053,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.1944555828724138</v>
+        <v>0.1945</v>
       </c>
       <c r="C57">
-        <v>0.1972060368705121</v>
+        <v>0.1972</v>
       </c>
       <c r="D57">
-        <v>0.3129496402877697</v>
+        <v>0.3129</v>
       </c>
       <c r="E57">
-        <v>0.8996171603008141</v>
+        <v>0.8996</v>
       </c>
       <c r="F57">
-        <v>314.9722688304263</v>
+        <v>314.9723</v>
       </c>
       <c r="G57">
-        <v>152.3469528024018</v>
+        <v>152.347</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2083,22 +2083,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.4141160518221578</v>
+        <v>0.4141</v>
       </c>
       <c r="C58">
-        <v>0.4270916605904978</v>
+        <v>0.4271</v>
       </c>
       <c r="D58">
-        <v>0.005882352941176554</v>
+        <v>0.0059</v>
       </c>
       <c r="E58">
-        <v>0.7310380474646212</v>
+        <v>0.731</v>
       </c>
       <c r="F58">
-        <v>2999.652668049377</v>
+        <v>2999.6527</v>
       </c>
       <c r="G58">
-        <v>2093.345443730012</v>
+        <v>2093.3454</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2113,22 +2113,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.4494502312709366</v>
+        <v>0.4495</v>
       </c>
       <c r="C59">
-        <v>0.4576044455780459</v>
+        <v>0.4576</v>
       </c>
       <c r="D59">
-        <v>0.009345794392523497</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E59">
-        <v>0.7003044013913833</v>
+        <v>0.7003</v>
       </c>
       <c r="F59">
-        <v>2201.283027972432</v>
+        <v>2201.283</v>
       </c>
       <c r="G59">
-        <v>1519.520657862692</v>
+        <v>1519.5207</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.4964152368348642</v>
+        <v>0.4964</v>
       </c>
       <c r="C60">
-        <v>0.5170670019461072</v>
+        <v>0.5171</v>
       </c>
       <c r="D60">
-        <v>0.01052631578947374</v>
+        <v>0.0105</v>
       </c>
       <c r="E60">
-        <v>0.6871361893500151</v>
+        <v>0.6871</v>
       </c>
       <c r="F60">
-        <v>7647.375165542444</v>
+        <v>7647.3752</v>
       </c>
       <c r="G60">
-        <v>6785.959553568397</v>
+        <v>6785.9596</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2173,22 +2173,22 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.5030900087191345</v>
+        <v>0.5031</v>
       </c>
       <c r="C61">
-        <v>0.5242080735752424</v>
+        <v>0.5242</v>
       </c>
       <c r="D61">
-        <v>0.01123595505617984</v>
+        <v>0.0112</v>
       </c>
       <c r="E61">
-        <v>0.6852201477110609</v>
+        <v>0.6852</v>
       </c>
       <c r="F61">
-        <v>6190.801521584344</v>
+        <v>6190.8015</v>
       </c>
       <c r="G61">
-        <v>5474.545469076982</v>
+        <v>5474.5455</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2203,22 +2203,22 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.740264048309918</v>
+        <v>0.7403</v>
       </c>
       <c r="C62">
-        <v>0.8763076026486629</v>
+        <v>0.8763</v>
       </c>
       <c r="D62">
-        <v>0.002717391304347816</v>
+        <v>0.0027</v>
       </c>
       <c r="E62">
-        <v>0.5724616495142405</v>
+        <v>0.5725</v>
       </c>
       <c r="F62">
-        <v>9866.08010182794</v>
+        <v>9866.080099999999</v>
       </c>
       <c r="G62">
-        <v>9436.320535329152</v>
+        <v>9436.3205</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.6955521829464071</v>
+        <v>0.6956</v>
       </c>
       <c r="C63">
-        <v>0.7875963890223526</v>
+        <v>0.7876</v>
       </c>
       <c r="D63">
-        <v>0.0030120481927711</v>
+        <v>0.003</v>
       </c>
       <c r="E63">
-        <v>0.5496356998915829</v>
+        <v>0.5496</v>
       </c>
       <c r="F63">
-        <v>12138.91622989328</v>
+        <v>12138.9162</v>
       </c>
       <c r="G63">
-        <v>11765.68573265038</v>
+        <v>11765.6857</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.6870953525218962</v>
+        <v>0.6871</v>
       </c>
       <c r="C64">
-        <v>0.7715125440140439</v>
+        <v>0.7715</v>
       </c>
       <c r="D64">
-        <v>0.003174603174603163</v>
+        <v>0.0032</v>
       </c>
       <c r="E64">
-        <v>0.5235282876976103</v>
+        <v>0.5235</v>
       </c>
       <c r="F64">
-        <v>12877.40498723332</v>
+        <v>12877.405</v>
       </c>
       <c r="G64">
-        <v>12394.04354065074</v>
+        <v>12394.0435</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2293,22 +2293,22 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.680550257400802</v>
+        <v>0.6806</v>
       </c>
       <c r="C65">
-        <v>0.7583672917843571</v>
+        <v>0.7584</v>
       </c>
       <c r="D65">
-        <v>0.003460207612456735</v>
+        <v>0.0035</v>
       </c>
       <c r="E65">
-        <v>0.5327618310627558</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="F65">
-        <v>15697.68836585553</v>
+        <v>15697.6884</v>
       </c>
       <c r="G65">
-        <v>15292.54523848155</v>
+        <v>15292.5452</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2323,22 +2323,22 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.6694001216782339</v>
+        <v>0.6694</v>
       </c>
       <c r="C66">
-        <v>0.7377269598144657</v>
+        <v>0.7377</v>
       </c>
       <c r="D66">
-        <v>0.003521126760563368</v>
+        <v>0.0035</v>
       </c>
       <c r="E66">
-        <v>0.5277072926569645</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="F66">
-        <v>15996.1099406975</v>
+        <v>15996.1099</v>
       </c>
       <c r="G66">
-        <v>15450.30686030979</v>
+        <v>15450.3069</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2353,22 +2353,22 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.728138217275485</v>
+        <v>0.7281</v>
       </c>
       <c r="C67">
-        <v>0.824736340017622</v>
+        <v>0.8247</v>
       </c>
       <c r="D67">
-        <v>0.002816901408450694</v>
+        <v>0.0028</v>
       </c>
       <c r="E67">
-        <v>0.5880163480967416</v>
+        <v>0.588</v>
       </c>
       <c r="F67">
-        <v>10437.243057093</v>
+        <v>10437.2431</v>
       </c>
       <c r="G67">
-        <v>10270.35313098156</v>
+        <v>10270.3531</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.6861023871875316</v>
+        <v>0.6861</v>
       </c>
       <c r="C68">
-        <v>0.7606361031790457</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="D68">
-        <v>0.003194888178913727</v>
+        <v>0.0032</v>
       </c>
       <c r="E68">
-        <v>0.5647684563476402</v>
+        <v>0.5648</v>
       </c>
       <c r="F68">
-        <v>13040.5193784329</v>
+        <v>13040.5194</v>
       </c>
       <c r="G68">
-        <v>12852.9351592142</v>
+        <v>12852.9352</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2413,22 +2413,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.6848088904889404</v>
+        <v>0.6848</v>
       </c>
       <c r="C69">
-        <v>0.7545114033842889</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="D69">
-        <v>0.003484320557491277</v>
+        <v>0.0035</v>
       </c>
       <c r="E69">
-        <v>0.539660121631191</v>
+        <v>0.5397</v>
       </c>
       <c r="F69">
-        <v>14763.08537819271</v>
+        <v>14763.0854</v>
       </c>
       <c r="G69">
-        <v>14603.99344995004</v>
+        <v>14603.9934</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2443,22 +2443,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.6623456939052156</v>
+        <v>0.6623</v>
       </c>
       <c r="C70">
-        <v>0.7317433854240678</v>
+        <v>0.7317</v>
       </c>
       <c r="D70">
-        <v>0.003759398496240521</v>
+        <v>0.0038</v>
       </c>
       <c r="E70">
-        <v>0.5406441725685208</v>
+        <v>0.5406</v>
       </c>
       <c r="F70">
-        <v>17030.5613522556</v>
+        <v>17030.5614</v>
       </c>
       <c r="G70">
-        <v>16704.36200221965</v>
+        <v>16704.362</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2473,22 +2473,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.6564187393822235</v>
+        <v>0.6564</v>
       </c>
       <c r="C71">
-        <v>0.7290642671287271</v>
+        <v>0.7291</v>
       </c>
       <c r="D71">
-        <v>0.00408163265306121</v>
+        <v>0.0041</v>
       </c>
       <c r="E71">
-        <v>0.5374425634416499</v>
+        <v>0.5374</v>
       </c>
       <c r="F71">
-        <v>19399.11333156067</v>
+        <v>19399.1133</v>
       </c>
       <c r="G71">
-        <v>19017.56494599545</v>
+        <v>19017.5649</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.7423983397076411</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="C72">
-        <v>0.8996902468506707</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="D72">
-        <v>0.002631578947368412</v>
+        <v>0.0026</v>
       </c>
       <c r="E72">
-        <v>0.5461482831335013</v>
+        <v>0.5461</v>
       </c>
       <c r="F72">
-        <v>8599.946743738725</v>
+        <v>8599.9467</v>
       </c>
       <c r="G72">
-        <v>8022.322379561977</v>
+        <v>8022.3224</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2533,22 +2533,22 @@
         </is>
       </c>
       <c r="B73">
-        <v>0.6681989298545548</v>
+        <v>0.6682</v>
       </c>
       <c r="C73">
-        <v>0.7311679370504975</v>
+        <v>0.7312</v>
       </c>
       <c r="D73">
-        <v>0.003484320557491277</v>
+        <v>0.0035</v>
       </c>
       <c r="E73">
-        <v>0.5599065433859955</v>
+        <v>0.5599</v>
       </c>
       <c r="F73">
-        <v>11869.20846020256</v>
+        <v>11869.2085</v>
       </c>
       <c r="G73">
-        <v>11665.51968964419</v>
+        <v>11665.5197</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.7021726688462135</v>
+        <v>0.7022</v>
       </c>
       <c r="C74">
-        <v>0.7907531416296912</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="D74">
-        <v>0.003484320557491277</v>
+        <v>0.0035</v>
       </c>
       <c r="E74">
-        <v>0.5305162030998446</v>
+        <v>0.5305</v>
       </c>
       <c r="F74">
-        <v>12772.66115045584</v>
+        <v>12772.6612</v>
       </c>
       <c r="G74">
-        <v>12663.04249426754</v>
+        <v>12663.0425</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2593,22 +2593,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.6835991721003815</v>
+        <v>0.6836</v>
       </c>
       <c r="C75">
-        <v>0.7544720730862731</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="D75">
-        <v>0.003484320557491277</v>
+        <v>0.0035</v>
       </c>
       <c r="E75">
-        <v>0.524770943127599</v>
+        <v>0.5248</v>
       </c>
       <c r="F75">
-        <v>15660.52282704409</v>
+        <v>15660.5228</v>
       </c>
       <c r="G75">
-        <v>15338.26323257929</v>
+        <v>15338.2632</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.6741049744519303</v>
+        <v>0.6741</v>
       </c>
       <c r="C76">
-        <v>0.7690865307656337</v>
+        <v>0.7691</v>
       </c>
       <c r="D76">
-        <v>0.004065040650406417</v>
+        <v>0.0041</v>
       </c>
       <c r="E76">
-        <v>0.5257809345460873</v>
+        <v>0.5258</v>
       </c>
       <c r="F76">
-        <v>18247.93854969901</v>
+        <v>18247.9385</v>
       </c>
       <c r="G76">
-        <v>17955.74639356063</v>
+        <v>17955.7464</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2653,22 +2653,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.5114307538639662</v>
+        <v>0.5114</v>
       </c>
       <c r="C77">
-        <v>0.5388277610547457</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="D77">
-        <v>0.008733624454148596</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="E77">
-        <v>0.6251557672651281</v>
+        <v>0.6252</v>
       </c>
       <c r="F77">
-        <v>1339.342024813101</v>
+        <v>1339.342</v>
       </c>
       <c r="G77">
-        <v>1359.383505049674</v>
+        <v>1359.3835</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2683,22 +2683,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.4118804653554831</v>
+        <v>0.4119</v>
       </c>
       <c r="C78">
-        <v>0.4254367675755902</v>
+        <v>0.4254</v>
       </c>
       <c r="D78">
-        <v>0.009132420091324331</v>
+        <v>0.0091</v>
       </c>
       <c r="E78">
-        <v>0.6130660458571386</v>
+        <v>0.6131</v>
       </c>
       <c r="F78">
-        <v>689.4017673668845</v>
+        <v>689.4018</v>
       </c>
       <c r="G78">
-        <v>701.401661464827</v>
+        <v>701.4017</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2713,22 +2713,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.5415423395610094</v>
+        <v>0.5415</v>
       </c>
       <c r="C79">
-        <v>0.5931074922083285</v>
+        <v>0.5931</v>
       </c>
       <c r="D79">
-        <v>0.007246376811594178</v>
+        <v>0.0072</v>
       </c>
       <c r="E79">
-        <v>0.5518983592368818</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="F79">
-        <v>5388.470527143162</v>
+        <v>5388.4705</v>
       </c>
       <c r="G79">
-        <v>5291.792985089463</v>
+        <v>5291.793</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.5707840102414113</v>
+        <v>0.5708</v>
       </c>
       <c r="C80">
-        <v>0.6255504685843173</v>
+        <v>0.6256</v>
       </c>
       <c r="D80">
-        <v>0.007246376811594178</v>
+        <v>0.0072</v>
       </c>
       <c r="E80">
-        <v>0.5379301669967399</v>
+        <v>0.5379</v>
       </c>
       <c r="F80">
-        <v>4128.238254805274</v>
+        <v>4128.2383</v>
       </c>
       <c r="G80">
-        <v>4056.532893944158</v>
+        <v>4056.5329</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2773,22 +2773,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.5542822196863642</v>
+        <v>0.5543</v>
       </c>
       <c r="C81">
-        <v>0.5862318484363185</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="D81">
-        <v>0.01249999999999996</v>
+        <v>0.0125</v>
       </c>
       <c r="E81">
-        <v>0.5312260328231524</v>
+        <v>0.5312</v>
       </c>
       <c r="F81">
-        <v>6716.643618911213</v>
+        <v>6716.6436</v>
       </c>
       <c r="G81">
-        <v>6788.317945412428</v>
+        <v>6788.3179</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -2803,22 +2803,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.4805552154136764</v>
+        <v>0.4806</v>
       </c>
       <c r="C82">
-        <v>0.5187200340188547</v>
+        <v>0.5187</v>
       </c>
       <c r="D82">
-        <v>0.008510638297872309</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E82">
-        <v>0.6504622093110144</v>
+        <v>0.6505</v>
       </c>
       <c r="F82">
-        <v>985.1073946611696</v>
+        <v>985.1074</v>
       </c>
       <c r="G82">
-        <v>1007.295334992964</v>
+        <v>1007.2953</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -2833,22 +2833,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.6105102129306967</v>
+        <v>0.6105</v>
       </c>
       <c r="C83">
-        <v>0.6652950682089606</v>
+        <v>0.6653</v>
       </c>
       <c r="D83">
-        <v>0.004694835680751156</v>
+        <v>0.0047</v>
       </c>
       <c r="E83">
-        <v>0.5645924197828823</v>
+        <v>0.5646</v>
       </c>
       <c r="F83">
-        <v>6078.627322828359</v>
+        <v>6078.6273</v>
       </c>
       <c r="G83">
-        <v>6152.025190431131</v>
+        <v>6152.0252</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.5181481027509064</v>
+        <v>0.5181</v>
       </c>
       <c r="C84">
-        <v>0.5591826175760222</v>
+        <v>0.5592</v>
       </c>
       <c r="D84">
-        <v>0.008333333333333304</v>
+        <v>0.0083</v>
       </c>
       <c r="E84">
-        <v>0.5614056377016491</v>
+        <v>0.5614</v>
       </c>
       <c r="F84">
-        <v>4122.911956690117</v>
+        <v>4122.912</v>
       </c>
       <c r="G84">
-        <v>4178.916516582163</v>
+        <v>4178.9165</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -2893,22 +2893,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.5635590831374906</v>
+        <v>0.5636</v>
       </c>
       <c r="C85">
-        <v>0.6404679446422544</v>
+        <v>0.6405</v>
       </c>
       <c r="D85">
-        <v>0.008620689655172384</v>
+        <v>0.0086</v>
       </c>
       <c r="E85">
-        <v>0.5117566717631404</v>
+        <v>0.5118</v>
       </c>
       <c r="F85">
-        <v>3680.598527287018</v>
+        <v>3680.5985</v>
       </c>
       <c r="G85">
-        <v>3754.897960774414</v>
+        <v>3754.898</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -2923,22 +2923,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.5202223857002221</v>
+        <v>0.5202</v>
       </c>
       <c r="C86">
-        <v>0.5596316641168951</v>
+        <v>0.5596</v>
       </c>
       <c r="D86">
-        <v>0.008771929824561372</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E86">
-        <v>0.5113749930559139</v>
+        <v>0.5114</v>
       </c>
       <c r="F86">
-        <v>2973.529489849407</v>
+        <v>2973.5295</v>
       </c>
       <c r="G86">
-        <v>3038.915012125166</v>
+        <v>3038.915</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -2953,22 +2953,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.2218593121807446</v>
+        <v>0.2219</v>
       </c>
       <c r="C87">
-        <v>0.2313448667385892</v>
+        <v>0.2313</v>
       </c>
       <c r="D87">
-        <v>0.1473087818696885</v>
+        <v>0.1473</v>
       </c>
       <c r="E87">
-        <v>0.8004019692824341</v>
+        <v>0.8004</v>
       </c>
       <c r="F87">
-        <v>110.7366096247123</v>
+        <v>110.7366</v>
       </c>
       <c r="G87">
-        <v>113.6106008328473</v>
+        <v>113.6106</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.1731857799198217</v>
+        <v>0.1732</v>
       </c>
       <c r="C88">
-        <v>0.1756412376969962</v>
+        <v>0.1756</v>
       </c>
       <c r="D88">
-        <v>0.104815864022663</v>
+        <v>0.1048</v>
       </c>
       <c r="E88">
-        <v>0.7907499963947952</v>
+        <v>0.7907</v>
       </c>
       <c r="F88">
-        <v>55.53869456049711</v>
+        <v>55.5387</v>
       </c>
       <c r="G88">
-        <v>57.01158040123023</v>
+        <v>57.0116</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3013,22 +3013,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.1887354016544358</v>
+        <v>0.1887</v>
       </c>
       <c r="C89">
-        <v>0.1878984661617767</v>
+        <v>0.1879</v>
       </c>
       <c r="D89">
-        <v>0.06042296072507553</v>
+        <v>0.0604</v>
       </c>
       <c r="E89">
-        <v>0.7407739533662432</v>
+        <v>0.7408</v>
       </c>
       <c r="F89">
-        <v>52.96237266774146</v>
+        <v>52.9624</v>
       </c>
       <c r="G89">
-        <v>54.55461900670437</v>
+        <v>54.5546</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3043,22 +3043,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.2179751285634675</v>
+        <v>0.218</v>
       </c>
       <c r="C90">
-        <v>0.2494362703886628</v>
+        <v>0.2494</v>
       </c>
       <c r="D90">
-        <v>0.04635761589403981</v>
+        <v>0.0464</v>
       </c>
       <c r="E90">
-        <v>0.7110960263734055</v>
+        <v>0.7111</v>
       </c>
       <c r="F90">
-        <v>69.87220111418628</v>
+        <v>69.87220000000001</v>
       </c>
       <c r="G90">
-        <v>72.38908352212189</v>
+        <v>72.3891</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.2077688264809099</v>
+        <v>0.2078</v>
       </c>
       <c r="C91">
-        <v>0.2324665531190459</v>
+        <v>0.2325</v>
       </c>
       <c r="D91">
-        <v>0.02649006622516547</v>
+        <v>0.0265</v>
       </c>
       <c r="E91">
-        <v>0.710807694954015</v>
+        <v>0.7108</v>
       </c>
       <c r="F91">
-        <v>55.88989913729959</v>
+        <v>55.8899</v>
       </c>
       <c r="G91">
-        <v>57.90516085259626</v>
+        <v>57.9052</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.8017853594975651</v>
+        <v>0.8018</v>
       </c>
       <c r="C92">
-        <v>0.9958779120659593</v>
+        <v>0.9959</v>
       </c>
       <c r="D92">
-        <v>0.002770083102493065</v>
+        <v>0.0028</v>
       </c>
       <c r="E92">
-        <v>0.5586664793032894</v>
+        <v>0.5587</v>
       </c>
       <c r="F92">
-        <v>8379.647977822477</v>
+        <v>8379.647999999999</v>
       </c>
       <c r="G92">
-        <v>8006.766889601686</v>
+        <v>8006.7669</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3133,22 +3133,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.7330713848712881</v>
+        <v>0.7331</v>
       </c>
       <c r="C93">
-        <v>0.8588423513136216</v>
+        <v>0.8588</v>
       </c>
       <c r="D93">
-        <v>0.003003003003002992</v>
+        <v>0.003</v>
       </c>
       <c r="E93">
-        <v>0.5286201386605701</v>
+        <v>0.5286</v>
       </c>
       <c r="F93">
-        <v>10018.75819678872</v>
+        <v>10018.7582</v>
       </c>
       <c r="G93">
-        <v>9705.912482728687</v>
+        <v>9705.9125</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3163,22 +3163,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.6946961035091672</v>
+        <v>0.6947</v>
       </c>
       <c r="C94">
-        <v>0.792171995252697</v>
+        <v>0.7922</v>
       </c>
       <c r="D94">
-        <v>0.003215434083601274</v>
+        <v>0.0032</v>
       </c>
       <c r="E94">
-        <v>0.5287762318438064</v>
+        <v>0.5288</v>
       </c>
       <c r="F94">
-        <v>12004.13084836257</v>
+        <v>12004.1308</v>
       </c>
       <c r="G94">
-        <v>11762.37677133099</v>
+        <v>11762.3768</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.6776725764981013</v>
+        <v>0.6777</v>
       </c>
       <c r="C95">
-        <v>0.7677588844048073</v>
+        <v>0.7678</v>
       </c>
       <c r="D95">
-        <v>0.003344481605351158</v>
+        <v>0.0033</v>
       </c>
       <c r="E95">
-        <v>0.5305848618877839</v>
+        <v>0.5306</v>
       </c>
       <c r="F95">
-        <v>13070.42240491467</v>
+        <v>13070.4224</v>
       </c>
       <c r="G95">
-        <v>12630.73065277297</v>
+        <v>12630.7307</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.6759561759153938</v>
+        <v>0.676</v>
       </c>
       <c r="C96">
-        <v>0.7576294879365902</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="D96">
-        <v>0.003389830508474564</v>
+        <v>0.0034</v>
       </c>
       <c r="E96">
-        <v>0.5102072373325929</v>
+        <v>0.5102</v>
       </c>
       <c r="F96">
-        <v>12644.59605510548</v>
+        <v>12644.5961</v>
       </c>
       <c r="G96">
-        <v>12133.85287752254</v>
+        <v>12133.8529</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3253,22 +3253,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.7679933737182323</v>
+        <v>0.768</v>
       </c>
       <c r="C97">
-        <v>0.9325921203781984</v>
+        <v>0.9326</v>
       </c>
       <c r="D97">
-        <v>0.002881844380403448</v>
+        <v>0.0029</v>
       </c>
       <c r="E97">
-        <v>0.5919320598386367</v>
+        <v>0.5919</v>
       </c>
       <c r="F97">
-        <v>9248.773917142549</v>
+        <v>9248.7739</v>
       </c>
       <c r="G97">
-        <v>9055.249439058136</v>
+        <v>9055.249400000001</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.6964213221939062</v>
+        <v>0.6964</v>
       </c>
       <c r="C98">
-        <v>0.7863543211427402</v>
+        <v>0.7864</v>
       </c>
       <c r="D98">
-        <v>0.003215434083601274</v>
+        <v>0.0032</v>
       </c>
       <c r="E98">
-        <v>0.5544793886614015</v>
+        <v>0.5545</v>
       </c>
       <c r="F98">
-        <v>11564.54467562182</v>
+        <v>11564.5447</v>
       </c>
       <c r="G98">
-        <v>11473.20509881626</v>
+        <v>11473.2051</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.6818006177415028</v>
+        <v>0.6818</v>
       </c>
       <c r="C99">
-        <v>0.7928173923901218</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="D99">
-        <v>0.003424657534246563</v>
+        <v>0.0034</v>
       </c>
       <c r="E99">
-        <v>0.5413666696671778</v>
+        <v>0.5414</v>
       </c>
       <c r="F99">
-        <v>13405.89017178113</v>
+        <v>13405.8902</v>
       </c>
       <c r="G99">
-        <v>12948.48589871302</v>
+        <v>12948.4859</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.6589612719492682</v>
+        <v>0.659</v>
       </c>
       <c r="C100">
-        <v>0.7434723802832803</v>
+        <v>0.7435</v>
       </c>
       <c r="D100">
-        <v>0.003999999999999914</v>
+        <v>0.004</v>
       </c>
       <c r="E100">
-        <v>0.5401478383767063</v>
+        <v>0.5401</v>
       </c>
       <c r="F100">
-        <v>15546.71015599555</v>
+        <v>15546.7102</v>
       </c>
       <c r="G100">
-        <v>15587.70030411075</v>
+        <v>15587.7003</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3373,22 +3373,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.6482822963184525</v>
+        <v>0.6483</v>
       </c>
       <c r="C101">
-        <v>0.703796591943485</v>
+        <v>0.7038</v>
       </c>
       <c r="D101">
-        <v>0.004184100418410027</v>
+        <v>0.0042</v>
       </c>
       <c r="E101">
-        <v>0.5438129479204475</v>
+        <v>0.5438</v>
       </c>
       <c r="F101">
-        <v>18083.14326184584</v>
+        <v>18083.1433</v>
       </c>
       <c r="G101">
-        <v>18152.59665309022</v>
+        <v>18152.5967</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3403,22 +3403,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.6586431397270067</v>
+        <v>0.6586</v>
       </c>
       <c r="C102">
-        <v>0.7323421923046548</v>
+        <v>0.7323</v>
       </c>
       <c r="D102">
-        <v>0.003194888178913726</v>
+        <v>0.0032</v>
       </c>
       <c r="E102">
-        <v>0.6149727669457503</v>
+        <v>0.615</v>
       </c>
       <c r="F102">
-        <v>6827.122892154884</v>
+        <v>6827.1229</v>
       </c>
       <c r="G102">
-        <v>7060.112110699352</v>
+        <v>7060.1121</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3433,22 +3433,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.6982707655801554</v>
+        <v>0.6983</v>
       </c>
       <c r="C103">
-        <v>0.7870307801639929</v>
+        <v>0.787</v>
       </c>
       <c r="D103">
-        <v>0.003194888178913726</v>
+        <v>0.0032</v>
       </c>
       <c r="E103">
-        <v>0.5530339458260038</v>
+        <v>0.553</v>
       </c>
       <c r="F103">
-        <v>11532.49573157574</v>
+        <v>11532.4957</v>
       </c>
       <c r="G103">
-        <v>11451.88521636872</v>
+        <v>11451.8852</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.6737508191793735</v>
+        <v>0.6738</v>
       </c>
       <c r="C104">
-        <v>0.7567983252382946</v>
+        <v>0.7568</v>
       </c>
       <c r="D104">
-        <v>0.004184100418410027</v>
+        <v>0.0042</v>
       </c>
       <c r="E104">
-        <v>0.5474590537950876</v>
+        <v>0.5475</v>
       </c>
       <c r="F104">
-        <v>11211.3378475471</v>
+        <v>11211.3378</v>
       </c>
       <c r="G104">
-        <v>11377.87973080669</v>
+        <v>11377.8797</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.6572541369507533</v>
+        <v>0.6573</v>
       </c>
       <c r="C105">
-        <v>0.7113004384410816</v>
+        <v>0.7113</v>
       </c>
       <c r="D105">
-        <v>0.004184100418410027</v>
+        <v>0.0042</v>
       </c>
       <c r="E105">
-        <v>0.5032393900754706</v>
+        <v>0.5032</v>
       </c>
       <c r="F105">
-        <v>12223.29261664338</v>
+        <v>12223.2926</v>
       </c>
       <c r="G105">
-        <v>12434.05486078606</v>
+        <v>12434.0549</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3523,22 +3523,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.6421893553462217</v>
+        <v>0.6422</v>
       </c>
       <c r="C106">
-        <v>0.690477501129748</v>
+        <v>0.6905</v>
       </c>
       <c r="D106">
-        <v>0.004184100418410027</v>
+        <v>0.0042</v>
       </c>
       <c r="E106">
-        <v>0.5121455503932878</v>
+        <v>0.5121</v>
       </c>
       <c r="F106">
-        <v>16514.97987896248</v>
+        <v>16514.9799</v>
       </c>
       <c r="G106">
-        <v>16708.42895025712</v>
+        <v>16708.429</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.1243276154380504</v>
+        <v>0.1243</v>
       </c>
       <c r="C107">
-        <v>0.1235932812173392</v>
+        <v>0.1236</v>
       </c>
       <c r="D107">
-        <v>0.1634877384196185</v>
+        <v>0.1635</v>
       </c>
       <c r="E107">
-        <v>0.8555686044105596</v>
+        <v>0.8556</v>
       </c>
       <c r="F107">
-        <v>64.67088783660377</v>
+        <v>64.6709</v>
       </c>
       <c r="G107">
-        <v>65.45341102262371</v>
+        <v>65.4534</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.1401765361936728</v>
+        <v>0.1402</v>
       </c>
       <c r="C108">
-        <v>0.1389246758795996</v>
+        <v>0.1389</v>
       </c>
       <c r="D108">
-        <v>0.1189024390243904</v>
+        <v>0.1189</v>
       </c>
       <c r="E108">
-        <v>0.8235923186230559</v>
+        <v>0.8236</v>
       </c>
       <c r="F108">
-        <v>55.30246678789717</v>
+        <v>55.3025</v>
       </c>
       <c r="G108">
-        <v>56.17797050897484</v>
+        <v>56.178</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3613,22 +3613,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.1936590060957736</v>
+        <v>0.1937</v>
       </c>
       <c r="C109">
-        <v>0.1988370725619547</v>
+        <v>0.1988</v>
       </c>
       <c r="D109">
-        <v>0.1074074074074074</v>
+        <v>0.1074</v>
       </c>
       <c r="E109">
-        <v>0.7817356051325266</v>
+        <v>0.7817</v>
       </c>
       <c r="F109">
-        <v>79.61198901308741</v>
+        <v>79.61199999999999</v>
       </c>
       <c r="G109">
-        <v>81.57287731634722</v>
+        <v>81.5729</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3643,22 +3643,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.2602137245114483</v>
+        <v>0.2602</v>
       </c>
       <c r="C110">
-        <v>0.3264390112732282</v>
+        <v>0.3264</v>
       </c>
       <c r="D110">
-        <v>0.04444444444444442</v>
+        <v>0.0444</v>
       </c>
       <c r="E110">
-        <v>0.7709869178675361</v>
+        <v>0.771</v>
       </c>
       <c r="F110">
-        <v>59.75378832582069</v>
+        <v>59.7538</v>
       </c>
       <c r="G110">
-        <v>61.23317794834529</v>
+        <v>61.2332</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3673,22 +3673,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.1900245609915916</v>
+        <v>0.19</v>
       </c>
       <c r="C111">
-        <v>0.2802610602351012</v>
+        <v>0.2803</v>
       </c>
       <c r="D111">
-        <v>0.03333333333333328</v>
+        <v>0.0333</v>
       </c>
       <c r="E111">
-        <v>0.7707476382320653</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="F111">
-        <v>47.79872086163279</v>
+        <v>47.7987</v>
       </c>
       <c r="G111">
-        <v>48.98603303568055</v>
+        <v>48.986</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.3193505810285757</v>
+        <v>0.3194</v>
       </c>
       <c r="C112">
-        <v>0.3350706777503601</v>
+        <v>0.3351</v>
       </c>
       <c r="D112">
-        <v>0.1074074074074074</v>
+        <v>0.1074</v>
       </c>
       <c r="E112">
-        <v>0.8069284802972062</v>
+        <v>0.8069</v>
       </c>
       <c r="F112">
-        <v>233.0311015171158</v>
+        <v>233.0311</v>
       </c>
       <c r="G112">
-        <v>238.6476525413465</v>
+        <v>238.6477</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.4854781602773699</v>
+        <v>0.4855</v>
       </c>
       <c r="C113">
-        <v>0.5121117333031665</v>
+        <v>0.5121</v>
       </c>
       <c r="D113">
-        <v>0.006369426751592447</v>
+        <v>0.0064</v>
       </c>
       <c r="E113">
-        <v>0.629329893454895</v>
+        <v>0.6293</v>
       </c>
       <c r="F113">
-        <v>1520.707346402623</v>
+        <v>1520.7073</v>
       </c>
       <c r="G113">
-        <v>1582.89531038258</v>
+        <v>1582.8953</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -3763,22 +3763,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.3987527466843248</v>
+        <v>0.3988</v>
       </c>
       <c r="C114">
-        <v>0.4073166961949303</v>
+        <v>0.4073</v>
       </c>
       <c r="D114">
-        <v>0.006369426751592447</v>
+        <v>0.0064</v>
       </c>
       <c r="E114">
-        <v>0.6282234616815603</v>
+        <v>0.6282</v>
       </c>
       <c r="F114">
-        <v>1017.051220373054</v>
+        <v>1017.0512</v>
       </c>
       <c r="G114">
-        <v>1058.838667554473</v>
+        <v>1058.8387</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -3793,22 +3793,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.4979925173757855</v>
+        <v>0.498</v>
       </c>
       <c r="C115">
-        <v>0.535866686786896</v>
+        <v>0.5359</v>
       </c>
       <c r="D115">
-        <v>0.008928571428571397</v>
+        <v>0.0089</v>
       </c>
       <c r="E115">
-        <v>0.5547734846370841</v>
+        <v>0.5548</v>
       </c>
       <c r="F115">
-        <v>4358.946007419638</v>
+        <v>4358.946</v>
       </c>
       <c r="G115">
-        <v>4443.325342326332</v>
+        <v>4443.3253</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -3823,22 +3823,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.5144291814427213</v>
+        <v>0.5144</v>
       </c>
       <c r="C116">
-        <v>0.5403432699977374</v>
+        <v>0.5403</v>
       </c>
       <c r="D116">
-        <v>0.01234567901234563</v>
+        <v>0.0123</v>
       </c>
       <c r="E116">
-        <v>0.5428804564827783</v>
+        <v>0.5429</v>
       </c>
       <c r="F116">
-        <v>3689.861263452853</v>
+        <v>3689.8613</v>
       </c>
       <c r="G116">
-        <v>3769.386002276884</v>
+        <v>3769.386</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -3853,22 +3853,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.5336794869039955</v>
+        <v>0.5337</v>
       </c>
       <c r="C117">
-        <v>0.5662058895999544</v>
+        <v>0.5662</v>
       </c>
       <c r="D117">
-        <v>0.003816793893129825</v>
+        <v>0.0038</v>
       </c>
       <c r="E117">
-        <v>0.6493009759771941</v>
+        <v>0.6493</v>
       </c>
       <c r="F117">
-        <v>2584.050983847825</v>
+        <v>2584.051</v>
       </c>
       <c r="G117">
-        <v>2723.911055598171</v>
+        <v>2723.9111</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -3883,22 +3883,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.480945261670276</v>
+        <v>0.4809</v>
       </c>
       <c r="C118">
-        <v>0.5140060686745476</v>
+        <v>0.514</v>
       </c>
       <c r="D118">
-        <v>0.006097560975609843</v>
+        <v>0.0061</v>
       </c>
       <c r="E118">
-        <v>0.6353529228545164</v>
+        <v>0.6354</v>
       </c>
       <c r="F118">
-        <v>1357.240358243711</v>
+        <v>1357.2404</v>
       </c>
       <c r="G118">
-        <v>1433.848349830678</v>
+        <v>1433.8483</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.577191647747308</v>
+        <v>0.5772</v>
       </c>
       <c r="C119">
-        <v>0.6100752234719655</v>
+        <v>0.6101</v>
       </c>
       <c r="D119">
-        <v>0.007812500000000108</v>
+        <v>0.0078</v>
       </c>
       <c r="E119">
-        <v>0.5434027273190803</v>
+        <v>0.5434</v>
       </c>
       <c r="F119">
-        <v>4188.026411587002</v>
+        <v>4188.0264</v>
       </c>
       <c r="G119">
-        <v>4361.629911166098</v>
+        <v>4361.6299</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.5610460651401833</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="C120">
-        <v>0.5658655205136097</v>
+        <v>0.5659</v>
       </c>
       <c r="D120">
-        <v>0.00952380952380966</v>
+        <v>0.0095</v>
       </c>
       <c r="E120">
-        <v>0.542145061864803</v>
+        <v>0.5421</v>
       </c>
       <c r="F120">
-        <v>3152.540328990367</v>
+        <v>3152.5403</v>
       </c>
       <c r="G120">
-        <v>3281.785408525725</v>
+        <v>3281.7854</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.5519640355849954</v>
+        <v>0.552</v>
       </c>
       <c r="C121">
-        <v>0.5538216888250523</v>
+        <v>0.5538</v>
       </c>
       <c r="D121">
-        <v>0.01030927835051561</v>
+        <v>0.0103</v>
       </c>
       <c r="E121">
-        <v>0.5331173741595394</v>
+        <v>0.5331</v>
       </c>
       <c r="F121">
-        <v>2623.480801645769</v>
+        <v>2623.4808</v>
       </c>
       <c r="G121">
-        <v>2733.641806581275</v>
+        <v>2733.6418</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/databases/metricas_avaliacao_clusters.xlsx
+++ b/databases/metricas_avaliacao_clusters.xlsx
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.7369</v>
+        <v>0.7433</v>
       </c>
       <c r="C32">
-        <v>0.8487</v>
+        <v>0.8595</v>
       </c>
       <c r="D32">
         <v>0.0024</v>
       </c>
       <c r="E32">
-        <v>0.703</v>
+        <v>0.7044</v>
       </c>
       <c r="F32">
-        <v>9623.2817</v>
+        <v>9489.7192</v>
       </c>
       <c r="G32">
-        <v>11687.7616</v>
+        <v>11778.1964</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1333,22 +1333,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.7113</v>
+        <v>0.7155</v>
       </c>
       <c r="C33">
-        <v>0.8589</v>
+        <v>0.8739</v>
       </c>
       <c r="D33">
         <v>0.0025</v>
       </c>
       <c r="E33">
-        <v>0.6959</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="F33">
-        <v>10904.5283</v>
+        <v>10689.9666</v>
       </c>
       <c r="G33">
-        <v>12865.4901</v>
+        <v>12811.7698</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.6802</v>
+        <v>0.6838</v>
       </c>
       <c r="C34">
-        <v>0.7764</v>
+        <v>0.7814</v>
       </c>
       <c r="D34">
         <v>0.0028</v>
       </c>
       <c r="E34">
-        <v>0.7181999999999999</v>
+        <v>0.7178</v>
       </c>
       <c r="F34">
-        <v>14456.3274</v>
+        <v>14013.0562</v>
       </c>
       <c r="G34">
-        <v>17376.8525</v>
+        <v>17093.0674</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.6566</v>
+        <v>0.6595</v>
       </c>
       <c r="C35">
-        <v>0.7764</v>
+        <v>0.7709</v>
       </c>
       <c r="D35">
         <v>0.0028</v>
       </c>
       <c r="E35">
-        <v>0.7325</v>
+        <v>0.7331</v>
       </c>
       <c r="F35">
-        <v>14060.8879</v>
+        <v>13735.3619</v>
       </c>
       <c r="G35">
-        <v>16360.782</v>
+        <v>16383.1657</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.6552</v>
+        <v>0.6506</v>
       </c>
       <c r="C36">
-        <v>0.7571</v>
+        <v>0.7552</v>
       </c>
       <c r="D36">
         <v>0.0029</v>
       </c>
       <c r="E36">
-        <v>0.7305</v>
+        <v>0.7341</v>
       </c>
       <c r="F36">
-        <v>12959.0571</v>
+        <v>12208.1328</v>
       </c>
       <c r="G36">
-        <v>15106.3285</v>
+        <v>14569.3748</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6782</v>
+        <v>0.6817</v>
       </c>
       <c r="C37">
-        <v>0.7557</v>
+        <v>0.773</v>
       </c>
       <c r="D37">
         <v>0.0025</v>
       </c>
       <c r="E37">
-        <v>0.7372</v>
+        <v>0.7388</v>
       </c>
       <c r="F37">
-        <v>11756.3444</v>
+        <v>11556.862</v>
       </c>
       <c r="G37">
-        <v>12277.6114</v>
+        <v>12157.3333</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.6846</v>
+        <v>0.6894</v>
       </c>
       <c r="C38">
-        <v>0.7726</v>
+        <v>0.7803</v>
       </c>
       <c r="D38">
         <v>0.0028</v>
       </c>
       <c r="E38">
-        <v>0.7203000000000001</v>
+        <v>0.7202</v>
       </c>
       <c r="F38">
-        <v>14486.9392</v>
+        <v>14206.0958</v>
       </c>
       <c r="G38">
-        <v>16585.9092</v>
+        <v>16438.5569</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1513,22 +1513,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.6824</v>
+        <v>0.6837</v>
       </c>
       <c r="C39">
-        <v>0.7598</v>
+        <v>0.7712</v>
       </c>
       <c r="D39">
         <v>0.003</v>
       </c>
       <c r="E39">
-        <v>0.7146</v>
+        <v>0.7161</v>
       </c>
       <c r="F39">
-        <v>16558.1116</v>
+        <v>16406.4364</v>
       </c>
       <c r="G39">
-        <v>19649.5389</v>
+        <v>19483.941</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.6588000000000001</v>
+        <v>0.6542</v>
       </c>
       <c r="C40">
-        <v>0.736</v>
+        <v>0.7171</v>
       </c>
       <c r="D40">
         <v>0.0035</v>
       </c>
       <c r="E40">
-        <v>0.7217</v>
+        <v>0.722</v>
       </c>
       <c r="F40">
-        <v>19516.4771</v>
+        <v>19327.5299</v>
       </c>
       <c r="G40">
-        <v>23398.1633</v>
+        <v>23438.6146</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.5512</v>
+        <v>0.6388</v>
       </c>
       <c r="C41">
-        <v>0.5869</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="D41">
-        <v>0.0077</v>
+        <v>0.0042</v>
       </c>
       <c r="E41">
-        <v>0.7169</v>
+        <v>0.7189</v>
       </c>
       <c r="F41">
-        <v>21207.6393</v>
+        <v>21645.1416</v>
       </c>
       <c r="G41">
-        <v>25078.43</v>
+        <v>26312.4677</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1603,22 +1603,22 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.7134</v>
+        <v>0.6566</v>
       </c>
       <c r="C42">
-        <v>0.7992</v>
+        <v>0.7438</v>
       </c>
       <c r="D42">
-        <v>0.0024</v>
+        <v>0.0026</v>
       </c>
       <c r="E42">
-        <v>0.7225</v>
+        <v>0.7407</v>
       </c>
       <c r="F42">
-        <v>10846.1135</v>
+        <v>11161.3318</v>
       </c>
       <c r="G42">
-        <v>12622.9826</v>
+        <v>10815.5723</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.6872</v>
+        <v>0.7366</v>
       </c>
       <c r="C43">
-        <v>0.8016</v>
+        <v>0.9604</v>
       </c>
       <c r="D43">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="E43">
-        <v>0.7144</v>
+        <v>0.6792</v>
       </c>
       <c r="F43">
-        <v>13930.8592</v>
+        <v>10776.9305</v>
       </c>
       <c r="G43">
-        <v>14734.6979</v>
+        <v>12435.003</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.6583</v>
+        <v>0.6633</v>
       </c>
       <c r="C44">
-        <v>0.7539</v>
+        <v>0.7439</v>
       </c>
       <c r="D44">
-        <v>0.0028</v>
+        <v>0.0033</v>
       </c>
       <c r="E44">
-        <v>0.7139</v>
+        <v>0.6986</v>
       </c>
       <c r="F44">
-        <v>13968.5876</v>
+        <v>15346.6967</v>
       </c>
       <c r="G44">
-        <v>16654.1821</v>
+        <v>17719.0867</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.6359</v>
+        <v>0.7056</v>
       </c>
       <c r="C45">
-        <v>0.7144</v>
+        <v>0.8426</v>
       </c>
       <c r="D45">
-        <v>0.004</v>
+        <v>0.0033</v>
       </c>
       <c r="E45">
-        <v>0.7143</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="F45">
-        <v>16204.6019</v>
+        <v>16507.69</v>
       </c>
       <c r="G45">
-        <v>19572.1464</v>
+        <v>18695.0854</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1723,22 +1723,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.6205000000000001</v>
+        <v>0.6801</v>
       </c>
       <c r="C46">
-        <v>0.6966</v>
+        <v>0.8018</v>
       </c>
       <c r="D46">
-        <v>0.004</v>
+        <v>0.0033</v>
       </c>
       <c r="E46">
-        <v>0.7158</v>
+        <v>0.7224</v>
       </c>
       <c r="F46">
-        <v>20013.0093</v>
+        <v>18038.6384</v>
       </c>
       <c r="G46">
-        <v>23618.5546</v>
+        <v>21821.852</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1753,22 +1753,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.1945</v>
+        <v>0.2647</v>
       </c>
       <c r="C47">
-        <v>0.1972</v>
+        <v>0.2955</v>
       </c>
       <c r="D47">
-        <v>0.3129</v>
+        <v>0.1007</v>
       </c>
       <c r="E47">
-        <v>0.8996</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="F47">
-        <v>314.9723</v>
+        <v>365.0935</v>
       </c>
       <c r="G47">
-        <v>152.347</v>
+        <v>317.0218</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.4199</v>
+        <v>0.4269</v>
       </c>
       <c r="C48">
-        <v>0.444</v>
+        <v>0.4847</v>
       </c>
       <c r="D48">
-        <v>0.0057</v>
+        <v>0.0123</v>
       </c>
       <c r="E48">
-        <v>0.7306</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F48">
-        <v>3356.6039</v>
+        <v>938.0682</v>
       </c>
       <c r="G48">
-        <v>2399.5433</v>
+        <v>781.2688000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.3244</v>
+        <v>0.3983</v>
       </c>
       <c r="C49">
-        <v>0.3535</v>
+        <v>0.5165</v>
       </c>
       <c r="D49">
-        <v>0.0057</v>
+        <v>0.0123</v>
       </c>
       <c r="E49">
-        <v>0.7297</v>
+        <v>0.7721</v>
       </c>
       <c r="F49">
-        <v>2241.6493</v>
+        <v>629.7597</v>
       </c>
       <c r="G49">
-        <v>1602.1815</v>
+        <v>524.1262</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1843,22 +1843,22 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.3909</v>
+        <v>0.4769</v>
       </c>
       <c r="C50">
-        <v>0.4222</v>
+        <v>0.5938</v>
       </c>
       <c r="D50">
         <v>0.008800000000000001</v>
       </c>
       <c r="E50">
-        <v>0.6927</v>
+        <v>0.7204</v>
       </c>
       <c r="F50">
-        <v>1885.5881</v>
+        <v>4913.2058</v>
       </c>
       <c r="G50">
-        <v>1336.0999</v>
+        <v>4515.9947</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.3866</v>
+        <v>0.3658</v>
       </c>
       <c r="C51">
-        <v>0.4179</v>
+        <v>0.3858</v>
       </c>
       <c r="D51">
-        <v>0.009900000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E51">
-        <v>0.6887</v>
+        <v>0.7196</v>
       </c>
       <c r="F51">
-        <v>1530.7891</v>
+        <v>3934.4744</v>
       </c>
       <c r="G51">
-        <v>1082.5759</v>
+        <v>3618.5444</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.1945</v>
+        <v>0.1173</v>
       </c>
       <c r="C52">
-        <v>0.1972</v>
+        <v>0.13</v>
       </c>
       <c r="D52">
-        <v>0.3129</v>
+        <v>0.1863</v>
       </c>
       <c r="E52">
-        <v>0.8996</v>
+        <v>0.9066</v>
       </c>
       <c r="F52">
-        <v>314.9723</v>
+        <v>235.3524</v>
       </c>
       <c r="G52">
-        <v>152.347</v>
+        <v>202.8687</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
         <v>0.1544</v>
       </c>
       <c r="D53">
-        <v>0.2446</v>
+        <v>0.1928</v>
       </c>
       <c r="E53">
-        <v>0.8817</v>
+        <v>0.8821</v>
       </c>
       <c r="F53">
-        <v>158.9421</v>
+        <v>158.7105</v>
       </c>
       <c r="G53">
-        <v>77.4258</v>
+        <v>137.3006</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -1963,22 +1963,22 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.102</v>
+        <v>0.1347</v>
       </c>
       <c r="C54">
-        <v>0.1096</v>
+        <v>0.155</v>
       </c>
       <c r="D54">
-        <v>0.0755</v>
+        <v>0.1007</v>
       </c>
       <c r="E54">
-        <v>0.8814</v>
+        <v>0.8536</v>
       </c>
       <c r="F54">
-        <v>105.9955</v>
+        <v>124.9332</v>
       </c>
       <c r="G54">
-        <v>51.6884</v>
+        <v>108.5949</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.1192</v>
+        <v>0.1131</v>
       </c>
       <c r="C55">
-        <v>0.1266</v>
+        <v>0.1205</v>
       </c>
       <c r="D55">
-        <v>0.0692</v>
+        <v>0.0755</v>
       </c>
       <c r="E55">
-        <v>0.8336</v>
+        <v>0.8534</v>
       </c>
       <c r="F55">
-        <v>91.1091</v>
+        <v>93.7236</v>
       </c>
       <c r="G55">
-        <v>49.0367</v>
+        <v>81.4945</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.1647</v>
+        <v>0.1214</v>
       </c>
       <c r="C56">
-        <v>0.1682</v>
+        <v>0.1287</v>
       </c>
       <c r="D56">
-        <v>0.034</v>
+        <v>0.0692</v>
       </c>
       <c r="E56">
-        <v>0.8139</v>
+        <v>0.8347</v>
       </c>
       <c r="F56">
-        <v>112.018</v>
+        <v>84.4432</v>
       </c>
       <c r="G56">
-        <v>74.2539</v>
+        <v>73.7462</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2053,22 +2053,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.1945</v>
+        <v>0.3116</v>
       </c>
       <c r="C57">
-        <v>0.1972</v>
+        <v>0.3101</v>
       </c>
       <c r="D57">
-        <v>0.3129</v>
+        <v>0.0692</v>
       </c>
       <c r="E57">
-        <v>0.8996</v>
+        <v>0.8839</v>
       </c>
       <c r="F57">
-        <v>314.9723</v>
+        <v>404.9591</v>
       </c>
       <c r="G57">
-        <v>152.347</v>
+        <v>355.3654</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2083,22 +2083,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.4141</v>
+        <v>0.4665</v>
       </c>
       <c r="C58">
-        <v>0.4271</v>
+        <v>0.4719</v>
       </c>
       <c r="D58">
-        <v>0.0059</v>
+        <v>0.0057</v>
       </c>
       <c r="E58">
-        <v>0.731</v>
+        <v>0.7355</v>
       </c>
       <c r="F58">
-        <v>2999.6527</v>
+        <v>2507.9127</v>
       </c>
       <c r="G58">
-        <v>2093.3454</v>
+        <v>1750.5207</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2113,22 +2113,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.4495</v>
+        <v>0.4269</v>
       </c>
       <c r="C59">
-        <v>0.4576</v>
+        <v>0.4368</v>
       </c>
       <c r="D59">
-        <v>0.009299999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="E59">
-        <v>0.7003</v>
+        <v>0.7342</v>
       </c>
       <c r="F59">
-        <v>2201.283</v>
+        <v>1686.7923</v>
       </c>
       <c r="G59">
-        <v>1519.5207</v>
+        <v>1175.3342</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.4964</v>
+        <v>0.4903</v>
       </c>
       <c r="C60">
-        <v>0.5171</v>
+        <v>0.5263</v>
       </c>
       <c r="D60">
-        <v>0.0105</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="E60">
-        <v>0.6871</v>
+        <v>0.7127</v>
       </c>
       <c r="F60">
-        <v>7647.3752</v>
+        <v>1345.852</v>
       </c>
       <c r="G60">
-        <v>6785.9596</v>
+        <v>932.0834</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2173,22 +2173,22 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.5031</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="C61">
-        <v>0.5242</v>
+        <v>0.5889</v>
       </c>
       <c r="D61">
-        <v>0.0112</v>
+        <v>0.0115</v>
       </c>
       <c r="E61">
-        <v>0.6852</v>
+        <v>0.6627</v>
       </c>
       <c r="F61">
-        <v>6190.8015</v>
+        <v>3572.6645</v>
       </c>
       <c r="G61">
-        <v>5474.5455</v>
+        <v>2957.7102</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.8018</v>
+        <v>0.8012</v>
       </c>
       <c r="C92">
         <v>0.9959</v>
@@ -3112,13 +3112,13 @@
         <v>0.0028</v>
       </c>
       <c r="E92">
-        <v>0.5587</v>
+        <v>0.5614</v>
       </c>
       <c r="F92">
-        <v>8379.647999999999</v>
+        <v>8432.0119</v>
       </c>
       <c r="G92">
-        <v>8006.7669</v>
+        <v>8116.1767</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3133,22 +3133,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.7331</v>
+        <v>0.7376</v>
       </c>
       <c r="C93">
-        <v>0.8588</v>
+        <v>0.8823</v>
       </c>
       <c r="D93">
         <v>0.003</v>
       </c>
       <c r="E93">
-        <v>0.5286</v>
+        <v>0.5251</v>
       </c>
       <c r="F93">
-        <v>10018.7582</v>
+        <v>9657.3763</v>
       </c>
       <c r="G93">
-        <v>9705.9125</v>
+        <v>9259.108399999999</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3163,22 +3163,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.6947</v>
+        <v>0.6938</v>
       </c>
       <c r="C94">
-        <v>0.7922</v>
+        <v>0.7895</v>
       </c>
       <c r="D94">
         <v>0.0032</v>
       </c>
       <c r="E94">
-        <v>0.5288</v>
+        <v>0.5326</v>
       </c>
       <c r="F94">
-        <v>12004.1308</v>
+        <v>12321.5879</v>
       </c>
       <c r="G94">
-        <v>11762.3768</v>
+        <v>12124.0091</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.6777</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="C95">
-        <v>0.7678</v>
+        <v>0.7792</v>
       </c>
       <c r="D95">
         <v>0.0033</v>
       </c>
       <c r="E95">
-        <v>0.5306</v>
+        <v>0.5276</v>
       </c>
       <c r="F95">
-        <v>13070.4224</v>
+        <v>12993.3997</v>
       </c>
       <c r="G95">
-        <v>12630.7307</v>
+        <v>12596.9458</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.676</v>
+        <v>0.6747</v>
       </c>
       <c r="C96">
-        <v>0.7576000000000001</v>
+        <v>0.7527</v>
       </c>
       <c r="D96">
         <v>0.0034</v>
       </c>
       <c r="E96">
-        <v>0.5102</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="F96">
-        <v>12644.5961</v>
+        <v>12305.9963</v>
       </c>
       <c r="G96">
-        <v>12133.8529</v>
+        <v>11806.9827</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3253,22 +3253,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.768</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="C97">
-        <v>0.9326</v>
+        <v>0.9522</v>
       </c>
       <c r="D97">
         <v>0.0029</v>
       </c>
       <c r="E97">
-        <v>0.5919</v>
+        <v>0.5939</v>
       </c>
       <c r="F97">
-        <v>9248.7739</v>
+        <v>9245.589900000001</v>
       </c>
       <c r="G97">
-        <v>9055.249400000001</v>
+        <v>8983.042100000001</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.6964</v>
+        <v>0.6933</v>
       </c>
       <c r="C98">
-        <v>0.7864</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="D98">
         <v>0.0032</v>
       </c>
       <c r="E98">
-        <v>0.5545</v>
+        <v>0.5557</v>
       </c>
       <c r="F98">
-        <v>11564.5447</v>
+        <v>11564.3364</v>
       </c>
       <c r="G98">
-        <v>11473.2051</v>
+        <v>11551.1856</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.6818</v>
+        <v>0.6849</v>
       </c>
       <c r="C99">
-        <v>0.7927999999999999</v>
+        <v>0.7582</v>
       </c>
       <c r="D99">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="E99">
-        <v>0.5414</v>
+        <v>0.543</v>
       </c>
       <c r="F99">
-        <v>13405.8902</v>
+        <v>13404.4989</v>
       </c>
       <c r="G99">
-        <v>12948.4859</v>
+        <v>13421.7968</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.659</v>
+        <v>0.6616</v>
       </c>
       <c r="C100">
-        <v>0.7435</v>
+        <v>0.7461</v>
       </c>
       <c r="D100">
         <v>0.004</v>
       </c>
       <c r="E100">
-        <v>0.5401</v>
+        <v>0.5431</v>
       </c>
       <c r="F100">
-        <v>15546.7102</v>
+        <v>15492.8523</v>
       </c>
       <c r="G100">
-        <v>15587.7003</v>
+        <v>15601.5364</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3373,22 +3373,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.6483</v>
+        <v>0.6508</v>
       </c>
       <c r="C101">
-        <v>0.7038</v>
+        <v>0.709</v>
       </c>
       <c r="D101">
-        <v>0.0042</v>
+        <v>0.0041</v>
       </c>
       <c r="E101">
-        <v>0.5438</v>
+        <v>0.5416</v>
       </c>
       <c r="F101">
-        <v>18083.1433</v>
+        <v>17930.0567</v>
       </c>
       <c r="G101">
-        <v>18152.5967</v>
+        <v>18090.64</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3403,22 +3403,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.6586</v>
+        <v>0.8111</v>
       </c>
       <c r="C102">
-        <v>0.7323</v>
+        <v>1.0247</v>
       </c>
       <c r="D102">
-        <v>0.0032</v>
+        <v>0.0027</v>
       </c>
       <c r="E102">
-        <v>0.615</v>
+        <v>0.5365</v>
       </c>
       <c r="F102">
-        <v>6827.1229</v>
+        <v>7579.43</v>
       </c>
       <c r="G102">
-        <v>7060.1121</v>
+        <v>7209.9997</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3433,22 +3433,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.6983</v>
+        <v>0.6964</v>
       </c>
       <c r="C103">
-        <v>0.787</v>
+        <v>0.7953</v>
       </c>
       <c r="D103">
         <v>0.0032</v>
       </c>
       <c r="E103">
-        <v>0.553</v>
+        <v>0.5581</v>
       </c>
       <c r="F103">
-        <v>11532.4957</v>
+        <v>11490.9142</v>
       </c>
       <c r="G103">
-        <v>11451.8852</v>
+        <v>11448.3297</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.6738</v>
+        <v>0.6731</v>
       </c>
       <c r="C104">
-        <v>0.7568</v>
+        <v>0.7511</v>
       </c>
       <c r="D104">
-        <v>0.0042</v>
+        <v>0.0032</v>
       </c>
       <c r="E104">
-        <v>0.5475</v>
+        <v>0.5097</v>
       </c>
       <c r="F104">
-        <v>11211.3378</v>
+        <v>11260.0546</v>
       </c>
       <c r="G104">
-        <v>11377.8797</v>
+        <v>11080.9456</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.6573</v>
+        <v>0.6355</v>
       </c>
       <c r="C105">
-        <v>0.7113</v>
+        <v>0.6827</v>
       </c>
       <c r="D105">
-        <v>0.0042</v>
+        <v>0.0046</v>
       </c>
       <c r="E105">
-        <v>0.5032</v>
+        <v>0.5084</v>
       </c>
       <c r="F105">
-        <v>12223.2926</v>
+        <v>12611.988</v>
       </c>
       <c r="G105">
-        <v>12434.0549</v>
+        <v>12727.4416</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3523,22 +3523,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.6422</v>
+        <v>0.6274</v>
       </c>
       <c r="C106">
-        <v>0.6905</v>
+        <v>0.6698</v>
       </c>
       <c r="D106">
-        <v>0.0042</v>
+        <v>0.0046</v>
       </c>
       <c r="E106">
-        <v>0.5121</v>
+        <v>0.5286</v>
       </c>
       <c r="F106">
-        <v>16514.9799</v>
+        <v>15829.9182</v>
       </c>
       <c r="G106">
-        <v>16708.429</v>
+        <v>15881.2579</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.1243</v>
+        <v>0.1238</v>
       </c>
       <c r="C107">
-        <v>0.1236</v>
+        <v>0.1231</v>
       </c>
       <c r="D107">
         <v>0.1635</v>
       </c>
       <c r="E107">
-        <v>0.8556</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="F107">
-        <v>64.6709</v>
+        <v>65.2711</v>
       </c>
       <c r="G107">
-        <v>65.4534</v>
+        <v>65.97150000000001</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.1402</v>
+        <v>0.1395</v>
       </c>
       <c r="C108">
-        <v>0.1389</v>
+        <v>0.1383</v>
       </c>
       <c r="D108">
         <v>0.1189</v>
       </c>
       <c r="E108">
-        <v>0.8236</v>
+        <v>0.8246</v>
       </c>
       <c r="F108">
-        <v>55.3025</v>
+        <v>55.8355</v>
       </c>
       <c r="G108">
-        <v>56.178</v>
+        <v>56.6511</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3613,22 +3613,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.1937</v>
+        <v>0.192</v>
       </c>
       <c r="C109">
-        <v>0.1988</v>
+        <v>0.1967</v>
       </c>
       <c r="D109">
         <v>0.1074</v>
       </c>
       <c r="E109">
-        <v>0.7817</v>
+        <v>0.7829</v>
       </c>
       <c r="F109">
-        <v>79.61199999999999</v>
+        <v>80.3638</v>
       </c>
       <c r="G109">
-        <v>81.5729</v>
+        <v>82.2788</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3643,22 +3643,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.2602</v>
+        <v>0.2739</v>
       </c>
       <c r="C110">
-        <v>0.3264</v>
+        <v>0.3432</v>
       </c>
       <c r="D110">
-        <v>0.0444</v>
+        <v>0.0407</v>
       </c>
       <c r="E110">
-        <v>0.771</v>
+        <v>0.7724</v>
       </c>
       <c r="F110">
-        <v>59.7538</v>
+        <v>60.3152</v>
       </c>
       <c r="G110">
-        <v>61.2332</v>
+        <v>61.7574</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3673,22 +3673,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="C111">
-        <v>0.2803</v>
+        <v>0.2942</v>
       </c>
       <c r="D111">
-        <v>0.0333</v>
+        <v>0.037</v>
       </c>
       <c r="E111">
-        <v>0.7707000000000001</v>
+        <v>0.7722</v>
       </c>
       <c r="F111">
-        <v>47.7987</v>
+        <v>48.2488</v>
       </c>
       <c r="G111">
-        <v>48.986</v>
+        <v>49.4073</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.3194</v>
+        <v>0.1238</v>
       </c>
       <c r="C112">
-        <v>0.3351</v>
+        <v>0.1231</v>
       </c>
       <c r="D112">
-        <v>0.1074</v>
+        <v>0.1635</v>
       </c>
       <c r="E112">
-        <v>0.8069</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="F112">
-        <v>233.0311</v>
+        <v>65.2711</v>
       </c>
       <c r="G112">
-        <v>238.6477</v>
+        <v>65.97150000000001</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.4855</v>
+        <v>0.4384</v>
       </c>
       <c r="C113">
-        <v>0.5121</v>
+        <v>0.4825</v>
       </c>
       <c r="D113">
-        <v>0.0064</v>
+        <v>0.0043</v>
       </c>
       <c r="E113">
-        <v>0.6293</v>
+        <v>0.6227</v>
       </c>
       <c r="F113">
-        <v>1520.7073</v>
+        <v>2536.8509</v>
       </c>
       <c r="G113">
-        <v>1582.8953</v>
+        <v>2655.4262</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -3763,22 +3763,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.3988</v>
+        <v>0.4609</v>
       </c>
       <c r="C114">
-        <v>0.4073</v>
+        <v>0.4805</v>
       </c>
       <c r="D114">
-        <v>0.0064</v>
+        <v>0.0073</v>
       </c>
       <c r="E114">
-        <v>0.6282</v>
+        <v>0.5939</v>
       </c>
       <c r="F114">
-        <v>1017.0512</v>
+        <v>1859.2921</v>
       </c>
       <c r="G114">
-        <v>1058.8387</v>
+        <v>1963.0127</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -3793,22 +3793,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.498</v>
+        <v>0.4355</v>
       </c>
       <c r="C115">
-        <v>0.5359</v>
+        <v>0.4717</v>
       </c>
       <c r="D115">
-        <v>0.0089</v>
+        <v>0.0076</v>
       </c>
       <c r="E115">
-        <v>0.5548</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="F115">
-        <v>4358.946</v>
+        <v>1406.3191</v>
       </c>
       <c r="G115">
-        <v>4443.3253</v>
+        <v>1485.088</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -3823,22 +3823,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.5144</v>
+        <v>0.5048</v>
       </c>
       <c r="C116">
-        <v>0.5403</v>
+        <v>0.5606</v>
       </c>
       <c r="D116">
-        <v>0.0123</v>
+        <v>0.0105</v>
       </c>
       <c r="E116">
-        <v>0.5429</v>
+        <v>0.5512</v>
       </c>
       <c r="F116">
-        <v>3689.8613</v>
+        <v>5516.4168</v>
       </c>
       <c r="G116">
-        <v>3769.386</v>
+        <v>5554.0657</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -3853,22 +3853,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.5337</v>
+        <v>0.4269</v>
       </c>
       <c r="C117">
-        <v>0.5662</v>
+        <v>0.4445</v>
       </c>
       <c r="D117">
-        <v>0.0038</v>
+        <v>0.0134</v>
       </c>
       <c r="E117">
-        <v>0.6493</v>
+        <v>0.7296</v>
       </c>
       <c r="F117">
-        <v>2584.051</v>
+        <v>759.8549</v>
       </c>
       <c r="G117">
-        <v>2723.9111</v>
+        <v>796.3116</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -3883,22 +3883,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.4809</v>
+        <v>0.6624</v>
       </c>
       <c r="C118">
-        <v>0.514</v>
+        <v>0.7712</v>
       </c>
       <c r="D118">
-        <v>0.0061</v>
+        <v>0.005</v>
       </c>
       <c r="E118">
-        <v>0.6354</v>
+        <v>0.5485</v>
       </c>
       <c r="F118">
-        <v>1357.2404</v>
+        <v>5700.3328</v>
       </c>
       <c r="G118">
-        <v>1433.8483</v>
+        <v>5600.6294</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.5772</v>
+        <v>0.5713</v>
       </c>
       <c r="C119">
-        <v>0.6101</v>
+        <v>0.6461</v>
       </c>
       <c r="D119">
-        <v>0.0078</v>
+        <v>0.0063</v>
       </c>
       <c r="E119">
-        <v>0.5434</v>
+        <v>0.5451</v>
       </c>
       <c r="F119">
-        <v>4188.0264</v>
+        <v>3859.7042</v>
       </c>
       <c r="G119">
-        <v>4361.6299</v>
+        <v>3792.4093</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.5610000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="C120">
-        <v>0.5659</v>
+        <v>0.6509</v>
       </c>
       <c r="D120">
-        <v>0.0095</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E120">
-        <v>0.5421</v>
+        <v>0.5417</v>
       </c>
       <c r="F120">
-        <v>3152.5403</v>
+        <v>4987.4155</v>
       </c>
       <c r="G120">
-        <v>3281.7854</v>
+        <v>5033.3766</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.552</v>
+        <v>0.5572</v>
       </c>
       <c r="C121">
-        <v>0.5538</v>
+        <v>0.573</v>
       </c>
       <c r="D121">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="E121">
-        <v>0.5331</v>
+        <v>0.541</v>
       </c>
       <c r="F121">
-        <v>2623.4808</v>
+        <v>4023.5829</v>
       </c>
       <c r="G121">
-        <v>2733.6418</v>
+        <v>4060.0974</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
